--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -617,10 +617,10 @@
         <v>3352</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7719</v>
+        <v>7432</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>6057</v>
+        <v>5770</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>4020</v>
@@ -652,10 +652,10 @@
         <v>3957</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>7149</v>
+        <v>6872</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>5184</v>
+        <v>4915</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>3696</v>
@@ -677,23 +677,23 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>T-17</t>
+          <t>T-03</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>106.47</v>
+        <v>124.45</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4634</v>
+        <v>4845</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>6997</v>
+        <v>6671</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4914</v>
+        <v>4280</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>4379</v>
+        <v>2795</v>
       </c>
       <c r="G7" s="8">
         <f>D7/1000</f>
@@ -712,23 +712,23 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>T-03</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>124.45</v>
+        <v>123.95</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>4845</v>
+        <v>5309</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>6971</v>
+        <v>6415</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>4568</v>
+        <v>3813</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>2795</v>
+        <v>3547</v>
       </c>
       <c r="G8" s="15">
         <f>D8/1000</f>
@@ -757,10 +757,10 @@
         <v>2500</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>6679</v>
+        <v>6411</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>5842</v>
+        <v>5573</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>4243</v>
@@ -782,23 +782,23 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>T-17</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>123.95</v>
+        <v>106.47</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>5309</v>
+        <v>4634</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>6676</v>
+        <v>6061</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>4073</v>
+        <v>4595</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>3547</v>
+        <v>4379</v>
       </c>
       <c r="G10" s="15">
         <f>D10/1000</f>
@@ -827,10 +827,10 @@
         <v>5346</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>6544</v>
+        <v>5872</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>4140</v>
+        <v>3697</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>2898</v>
@@ -852,23 +852,23 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>T-16</t>
+          <t>T-07</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>151.26</v>
+        <v>133.59</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>5633</v>
+        <v>4784</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>6397</v>
+        <v>5769</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>4066</v>
+        <v>3399</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>3546</v>
+        <v>2279</v>
       </c>
       <c r="G12" s="15">
         <f>D12/1000</f>
@@ -887,23 +887,23 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>133.59</v>
+        <v>99.23</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4784</v>
+        <v>4809</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>6055</v>
+        <v>5747</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3668</v>
+        <v>3357</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>2279</v>
+        <v>2842</v>
       </c>
       <c r="G13" s="8">
         <f>D13/1000</f>
@@ -922,23 +922,23 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>99.23</v>
+        <v>151.26</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>4809</v>
+        <v>5633</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>6046</v>
+        <v>5445</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>3656</v>
+        <v>3809</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>2842</v>
+        <v>3546</v>
       </c>
       <c r="G14" s="15">
         <f>D14/1000</f>
@@ -967,10 +967,10 @@
         <v>3658</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>5315</v>
+        <v>4983</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3550</v>
+        <v>3218</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>2908</v>
@@ -1002,10 +1002,10 @@
         <v>4270</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>5200</v>
+        <v>4939</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>3504</v>
+        <v>3235</v>
       </c>
       <c r="F16" s="14" t="n">
         <v>2214</v>
@@ -1037,10 +1037,10 @@
         <v>5776</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>5056</v>
+        <v>4768</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2524</v>
+        <v>2205</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>2045</v>
@@ -1060,39 +1060,39 @@
       <c r="J17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>T-06</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="12" t="n">
         <v>180.3</v>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="13" t="n">
         <v>5857</v>
       </c>
-      <c r="D18" s="21" t="n">
-        <v>4838</v>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>2302</v>
-      </c>
-      <c r="F18" s="21" t="n">
+      <c r="D18" s="14" t="n">
+        <v>4538</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F18" s="14" t="n">
         <v>1530</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="15">
         <f>D18/1000</f>
         <v/>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="15">
         <f>E18/1000</f>
         <v/>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="16">
         <f>IFERROR(D18/F18,"")</f>
         <v/>
       </c>
-      <c r="J18" s="24" t="inlineStr"/>
+      <c r="J18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1107,10 +1107,10 @@
         <v>4388</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>4750</v>
+        <v>4481</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2560</v>
+        <v>2291</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>2039</v>
@@ -1130,39 +1130,39 @@
       <c r="J19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>T-05</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="12" t="n">
         <v>130.25</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="13" t="n">
         <v>8274</v>
       </c>
-      <c r="D20" s="21" t="n">
-        <v>4687</v>
-      </c>
-      <c r="E20" s="21" t="n">
-        <v>2288</v>
-      </c>
-      <c r="F20" s="21" t="n">
+      <c r="D20" s="14" t="n">
+        <v>4386</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F20" s="14" t="n">
         <v>1498</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="15">
         <f>D20/1000</f>
         <v/>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="15">
         <f>E20/1000</f>
         <v/>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="16">
         <f>IFERROR(D20/F20,"")</f>
         <v/>
       </c>
-      <c r="J20" s="24" t="inlineStr"/>
+      <c r="J20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1177,10 +1177,10 @@
         <v>2565</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>4409</v>
+        <v>4080</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>3555</v>
+        <v>3223</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>2476</v>
@@ -1212,10 +1212,10 @@
         <v>2574</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>4320</v>
+        <v>3992</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>3055</v>
+        <v>2729</v>
       </c>
       <c r="F22" s="14" t="n">
         <v>2446</v>
@@ -1247,10 +1247,10 @@
         <v>4844</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>3995</v>
+        <v>3773</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>1594</v>
+        <v>1486</v>
       </c>
       <c r="F23" s="21" t="n">
         <v>1228</v>
@@ -1270,74 +1270,74 @@
       <c r="J23" s="24" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>T-19</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>177.46</v>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>5465</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>3704</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>969</v>
+      </c>
+      <c r="G24" s="22">
+        <f>D24/1000</f>
+        <v/>
+      </c>
+      <c r="H24" s="22">
+        <f>E24/1000</f>
+        <v/>
+      </c>
+      <c r="I24" s="23">
+        <f>IFERROR(D24/F24,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>T-10A</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B25" s="5" t="n">
         <v>25.3</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C25" s="6" t="n">
         <v>3448</v>
       </c>
-      <c r="D24" s="14" t="n">
-        <v>3790</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>2308</v>
-      </c>
-      <c r="F24" s="14" t="n">
+      <c r="D25" s="7" t="n">
+        <v>3514</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F25" s="7" t="n">
         <v>1527</v>
       </c>
-      <c r="G24" s="15">
-        <f>D24/1000</f>
-        <v/>
-      </c>
-      <c r="H24" s="15">
-        <f>E24/1000</f>
-        <v/>
-      </c>
-      <c r="I24" s="16">
-        <f>IFERROR(D24/F24,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>T-19</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>177.46</v>
-      </c>
-      <c r="C25" s="20" t="n">
-        <v>5465</v>
-      </c>
-      <c r="D25" s="21" t="n">
-        <v>3701</v>
-      </c>
-      <c r="E25" s="21" t="n">
-        <v>1578</v>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>969</v>
-      </c>
-      <c r="G25" s="22">
+      <c r="G25" s="8">
         <f>D25/1000</f>
         <v/>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="8">
         <f>E25/1000</f>
         <v/>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="9">
         <f>IFERROR(D25/F25,"")</f>
         <v/>
       </c>
-      <c r="J25" s="24" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
@@ -1352,10 +1352,10 @@
         <v>5252</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>3661</v>
+        <v>3384</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>1060</v>
+        <v>761</v>
       </c>
       <c r="F26" s="21" t="n">
         <v>567</v>
@@ -1387,10 +1387,10 @@
         <v>5481</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>3275</v>
+        <v>2899</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>1060</v>
+        <v>291</v>
       </c>
       <c r="F27" s="21" t="n">
         <v>291</v>
@@ -1422,10 +1422,10 @@
         <v>4052</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>3038</v>
+        <v>2830</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>1025</v>
+        <v>925</v>
       </c>
       <c r="F28" s="21" t="n">
         <v>767</v>
@@ -1457,10 +1457,10 @@
         <v>4418</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>2875</v>
+        <v>2597</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>685</v>
+        <v>563</v>
       </c>
       <c r="F29" s="21" t="n">
         <v>546</v>
@@ -1492,10 +1492,10 @@
         <v>4022</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>2466</v>
+        <v>2485</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>1068</v>
+        <v>959</v>
       </c>
       <c r="F30" s="21" t="n">
         <v>473</v>
@@ -1527,10 +1527,10 @@
         <v>3752</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>1994</v>
+        <v>2007</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>120</v>
+        <v>353</v>
       </c>
       <c r="F31" s="21" t="n">
         <v>121</v>
@@ -1562,10 +1562,10 @@
         <v>4288</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>1981</v>
+        <v>1307</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>374</v>
+        <v>142</v>
       </c>
       <c r="F32" s="21" t="n">
         <v>142</v>

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -617,10 +617,10 @@
         <v>3352</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7432</v>
+        <v>7956</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>5770</v>
+        <v>5867</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>4020</v>
@@ -652,10 +652,10 @@
         <v>3957</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6872</v>
+        <v>7607</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>4915</v>
+        <v>4984</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>3696</v>
@@ -687,10 +687,10 @@
         <v>4845</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>6671</v>
+        <v>7030</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4280</v>
+        <v>4345</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>2795</v>
@@ -712,23 +712,23 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>123.95</v>
+        <v>38.37</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>5309</v>
+        <v>2500</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>6415</v>
+        <v>6899</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>3813</v>
+        <v>5972</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>3547</v>
+        <v>4243</v>
       </c>
       <c r="G8" s="15">
         <f>D8/1000</f>
@@ -747,23 +747,23 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>38.37</v>
+        <v>123.95</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>2500</v>
+        <v>5309</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>6411</v>
+        <v>6841</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>5573</v>
+        <v>3836</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>4243</v>
+        <v>3547</v>
       </c>
       <c r="G9" s="8">
         <f>D9/1000</f>
@@ -792,10 +792,10 @@
         <v>4634</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>6061</v>
+        <v>6548</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>4595</v>
+        <v>4609</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>4379</v>
@@ -827,10 +827,10 @@
         <v>5346</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5872</v>
+        <v>6268</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3697</v>
+        <v>3709</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>2898</v>
@@ -852,23 +852,23 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>133.59</v>
+        <v>99.23</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>4784</v>
+        <v>4809</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>5769</v>
+        <v>6210</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>3399</v>
+        <v>3404</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2279</v>
+        <v>2842</v>
       </c>
       <c r="G12" s="15">
         <f>D12/1000</f>
@@ -887,23 +887,23 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-07</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>99.23</v>
+        <v>133.59</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4809</v>
+        <v>4784</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5747</v>
+        <v>5978</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3357</v>
+        <v>3445</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>2842</v>
+        <v>2279</v>
       </c>
       <c r="G13" s="8">
         <f>D13/1000</f>
@@ -932,10 +932,10 @@
         <v>5633</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>5445</v>
+        <v>5469</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>3809</v>
+        <v>3838</v>
       </c>
       <c r="F14" s="14" t="n">
         <v>3546</v>
@@ -955,60 +955,60 @@
       <c r="J14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>T-21</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>75.97</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>3658</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>4983</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>3218</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>2908</v>
-      </c>
-      <c r="G15" s="8">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>T-06</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="C15" s="20" t="n">
+        <v>5857</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>5285</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G15" s="22">
         <f>D15/1000</f>
         <v/>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="22">
         <f>E15/1000</f>
         <v/>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="23">
         <f>IFERROR(D15/F15,"")</f>
         <v/>
       </c>
-      <c r="J15" s="10" t="inlineStr"/>
+      <c r="J15" s="24" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>T-11A</t>
+          <t>T-21</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>77.29000000000001</v>
+        <v>75.97</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4270</v>
+        <v>3658</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>4939</v>
+        <v>5099</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2214</v>
+        <v>2908</v>
       </c>
       <c r="G16" s="15">
         <f>D16/1000</f>
@@ -1027,23 +1027,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>T-15</t>
+          <t>T-11A</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>200.37</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>5776</v>
+        <v>4270</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>4768</v>
+        <v>4990</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2205</v>
+        <v>3281</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>2045</v>
+        <v>2214</v>
       </c>
       <c r="G17" s="8">
         <f>D17/1000</f>
@@ -1060,60 +1060,60 @@
       <c r="J17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>T-06</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>180.3</v>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>5857</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>4538</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>1530</v>
-      </c>
-      <c r="G18" s="15">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>T-05</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="C18" s="20" t="n">
+        <v>8274</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>4815</v>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>2034</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>1498</v>
+      </c>
+      <c r="G18" s="22">
         <f>D18/1000</f>
         <v/>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="22">
         <f>E18/1000</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="23">
         <f>IFERROR(D18/F18,"")</f>
         <v/>
       </c>
-      <c r="J18" s="17" t="inlineStr"/>
+      <c r="J18" s="24" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>T-15</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>98.26000000000001</v>
+        <v>200.37</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>4388</v>
+        <v>5776</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>4481</v>
+        <v>4807</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2291</v>
+        <v>2220</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>2039</v>
+        <v>2045</v>
       </c>
       <c r="G19" s="8">
         <f>D19/1000</f>
@@ -1132,23 +1132,23 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>130.25</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>8274</v>
+        <v>4388</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>4386</v>
+        <v>4746</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>1988</v>
+        <v>2311</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1498</v>
+        <v>2039</v>
       </c>
       <c r="G20" s="15">
         <f>D20/1000</f>
@@ -1165,60 +1165,60 @@
       <c r="J20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>T-21R</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>2565</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>4080</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>3223</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>2476</v>
-      </c>
-      <c r="G21" s="8">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>T-19</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>177.46</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>5465</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>4633</v>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>1495</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>969</v>
+      </c>
+      <c r="G21" s="22">
         <f>D21/1000</f>
         <v/>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="22">
         <f>E21/1000</f>
         <v/>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="23">
         <f>IFERROR(D21/F21,"")</f>
         <v/>
       </c>
-      <c r="J21" s="10" t="inlineStr"/>
+      <c r="J21" s="24" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>T-21R</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>37.65</v>
+        <v>37.7</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>2574</v>
+        <v>2565</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>3992</v>
+        <v>4300</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>2729</v>
+        <v>3238</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>2446</v>
+        <v>2476</v>
       </c>
       <c r="G22" s="15">
         <f>D22/1000</f>
@@ -1235,109 +1235,109 @@
       <c r="J22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2574</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>4269</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>2446</v>
+      </c>
+      <c r="G23" s="8">
+        <f>D23/1000</f>
+        <v/>
+      </c>
+      <c r="H23" s="8">
+        <f>E23/1000</f>
+        <v/>
+      </c>
+      <c r="I23" s="9">
+        <f>IFERROR(D23/F23,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>T-10A</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>3448</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>4012</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>2046</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>1527</v>
+      </c>
+      <c r="G24" s="15">
+        <f>D24/1000</f>
+        <v/>
+      </c>
+      <c r="H24" s="15">
+        <f>E24/1000</f>
+        <v/>
+      </c>
+      <c r="I24" s="16">
+        <f>IFERROR(D24/F24,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="17" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>T-20</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B25" s="19" t="n">
         <v>135.58</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C25" s="20" t="n">
         <v>4844</v>
       </c>
-      <c r="D23" s="21" t="n">
-        <v>3773</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>1486</v>
-      </c>
-      <c r="F23" s="21" t="n">
+      <c r="D25" s="21" t="n">
+        <v>3918</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>1505</v>
+      </c>
+      <c r="F25" s="21" t="n">
         <v>1228</v>
       </c>
-      <c r="G23" s="22">
-        <f>D23/1000</f>
-        <v/>
-      </c>
-      <c r="H23" s="22">
-        <f>E23/1000</f>
-        <v/>
-      </c>
-      <c r="I23" s="23">
-        <f>IFERROR(D23/F23,"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="24" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>T-19</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n">
-        <v>177.46</v>
-      </c>
-      <c r="C24" s="20" t="n">
-        <v>5465</v>
-      </c>
-      <c r="D24" s="21" t="n">
-        <v>3704</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>1470</v>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>969</v>
-      </c>
-      <c r="G24" s="22">
-        <f>D24/1000</f>
-        <v/>
-      </c>
-      <c r="H24" s="22">
-        <f>E24/1000</f>
-        <v/>
-      </c>
-      <c r="I24" s="23">
-        <f>IFERROR(D24/F24,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>T-10A</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>3448</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>3514</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>2009</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>1527</v>
-      </c>
-      <c r="G25" s="8">
+      <c r="G25" s="22">
         <f>D25/1000</f>
         <v/>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="22">
         <f>E25/1000</f>
         <v/>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="23">
         <f>IFERROR(D25/F25,"")</f>
         <v/>
       </c>
-      <c r="J25" s="10" t="inlineStr"/>
+      <c r="J25" s="24" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
@@ -1352,10 +1352,10 @@
         <v>5252</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>3384</v>
+        <v>3781</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="F26" s="21" t="n">
         <v>567</v>
@@ -1377,23 +1377,23 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>T-09</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>182.48</v>
+        <v>78.38</v>
       </c>
       <c r="C27" s="20" t="n">
-        <v>5481</v>
+        <v>4052</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>2899</v>
+        <v>3296</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>291</v>
+        <v>953</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>291</v>
+        <v>767</v>
       </c>
       <c r="G27" s="22">
         <f>D27/1000</f>
@@ -1412,23 +1412,23 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>T-09</t>
         </is>
       </c>
       <c r="B28" s="19" t="n">
-        <v>78.38</v>
+        <v>182.48</v>
       </c>
       <c r="C28" s="20" t="n">
-        <v>4052</v>
+        <v>5481</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>2830</v>
+        <v>3009</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>925</v>
+        <v>292</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>767</v>
+        <v>291</v>
       </c>
       <c r="G28" s="22">
         <f>D28/1000</f>
@@ -1457,7 +1457,7 @@
         <v>4418</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>2597</v>
+        <v>2729</v>
       </c>
       <c r="E29" s="21" t="n">
         <v>563</v>
@@ -1492,10 +1492,10 @@
         <v>4022</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>2485</v>
+        <v>2647</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>959</v>
+        <v>978</v>
       </c>
       <c r="F30" s="21" t="n">
         <v>473</v>
@@ -1527,7 +1527,7 @@
         <v>3752</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>2007</v>
+        <v>2322</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>353</v>
@@ -1562,7 +1562,7 @@
         <v>4288</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>1307</v>
+        <v>1496</v>
       </c>
       <c r="E32" s="21" t="n">
         <v>142</v>

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA942CC-D3A7-4A76-9A36-31E3B12B11A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FC3FEC-9139-4795-BC13-06FAD367EA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34755" yWindow="2610" windowWidth="17625" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FC3FEC-9139-4795-BC13-06FAD367EA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9F7663-39DD-48D4-ADD7-A10282A245D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,18 +72,18 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
     <t>T-04</t>
   </si>
   <si>
     <t>T-08</t>
   </si>
   <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-07</t>
-  </si>
-  <si>
     <t>P-26</t>
   </si>
   <si>
@@ -93,52 +93,52 @@
     <t>T-10A</t>
   </si>
   <si>
+    <t>T-11A</t>
+  </si>
+  <si>
     <t>T-02</t>
   </si>
   <si>
-    <t>T-11A</t>
+    <t>T-17</t>
   </si>
   <si>
     <t>T-11</t>
   </si>
   <si>
+    <t>T-15</t>
+  </si>
+  <si>
+    <t>T-16</t>
+  </si>
+  <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-21</t>
+  </si>
+  <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-19</t>
+  </si>
+  <si>
+    <t>T-21R</t>
+  </si>
+  <si>
+    <t>A-01</t>
+  </si>
+  <si>
     <t>T-20</t>
   </si>
   <si>
-    <t>T-15</t>
-  </si>
-  <si>
-    <t>T-16</t>
-  </si>
-  <si>
-    <t>A-01</t>
-  </si>
-  <si>
-    <t>T-01</t>
-  </si>
-  <si>
-    <t>T-17</t>
-  </si>
-  <si>
-    <t>T-21</t>
-  </si>
-  <si>
-    <t>T-21R</t>
-  </si>
-  <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-06</t>
-  </si>
-  <si>
     <t>P-02</t>
   </si>
   <si>
     <t>T-10</t>
-  </si>
-  <si>
-    <t>T-19</t>
   </si>
   <si>
     <t>T-14</t>
@@ -736,31 +736,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>69.11</v>
+        <v>124.45</v>
       </c>
       <c r="C5" s="6">
-        <v>3352</v>
+        <v>4845</v>
       </c>
       <c r="D5" s="7">
-        <v>13492</v>
+        <v>13406</v>
       </c>
       <c r="E5" s="7">
-        <v>11435</v>
+        <v>6252</v>
       </c>
       <c r="F5" s="7">
-        <v>4020</v>
+        <v>2795</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G32" si="0">D5/1000</f>
-        <v>13.492000000000001</v>
+        <v>13.406000000000001</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H32" si="1">E5/1000</f>
-        <v>11.435</v>
+        <v>6.2519999999999998</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I32" si="2">IFERROR(D5/F5,"")</f>
-        <v>3.356218905472637</v>
+        <v>4.7964221824686941</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -769,31 +769,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="5">
-        <v>94.59</v>
+        <v>133.59</v>
       </c>
       <c r="C6" s="6">
-        <v>3957</v>
+        <v>4784</v>
       </c>
       <c r="D6" s="7">
-        <v>13491</v>
+        <v>13406</v>
       </c>
       <c r="E6" s="7">
-        <v>9009</v>
+        <v>3445</v>
       </c>
       <c r="F6" s="7">
-        <v>3696</v>
+        <v>2279</v>
       </c>
       <c r="G6" s="8">
         <f t="shared" si="0"/>
-        <v>13.491</v>
+        <v>13.406000000000001</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="1"/>
-        <v>9.0090000000000003</v>
+        <v>3.4449999999999998</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="2"/>
-        <v>3.6501623376623376</v>
+        <v>5.882404563405002</v>
       </c>
       <c r="J6" s="10"/>
     </row>
@@ -802,31 +802,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>124.45</v>
+        <v>69.11</v>
       </c>
       <c r="C7" s="6">
-        <v>4845</v>
+        <v>3352</v>
       </c>
       <c r="D7" s="7">
-        <v>13473</v>
+        <v>13229</v>
       </c>
       <c r="E7" s="7">
-        <v>6054</v>
+        <v>11171</v>
       </c>
       <c r="F7" s="7">
-        <v>2795</v>
+        <v>4020</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>13.473000000000001</v>
+        <v>13.228999999999999</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>6.0540000000000003</v>
+        <v>11.170999999999999</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>4.8203935599284433</v>
+        <v>3.2907960199004975</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -835,31 +835,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="5">
-        <v>133.59</v>
+        <v>94.59</v>
       </c>
       <c r="C8" s="6">
-        <v>4784</v>
+        <v>3957</v>
       </c>
       <c r="D8" s="7">
-        <v>13473</v>
+        <v>13228</v>
       </c>
       <c r="E8" s="7">
-        <v>5262</v>
+        <v>8942</v>
       </c>
       <c r="F8" s="7">
-        <v>2279</v>
+        <v>3696</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="0"/>
-        <v>13.473000000000001</v>
+        <v>13.228</v>
       </c>
       <c r="H8" s="8">
         <f t="shared" si="1"/>
-        <v>5.2619999999999996</v>
+        <v>8.9420000000000002</v>
       </c>
       <c r="I8" s="9">
         <f t="shared" si="2"/>
-        <v>5.9118034225537519</v>
+        <v>3.579004329004329</v>
       </c>
       <c r="J8" s="10"/>
     </row>
@@ -874,25 +874,25 @@
         <v>2500</v>
       </c>
       <c r="D9" s="14">
-        <v>11127</v>
+        <v>11059</v>
       </c>
       <c r="E9" s="14">
-        <v>7712</v>
+        <v>9315</v>
       </c>
       <c r="F9" s="14">
         <v>4243</v>
       </c>
       <c r="G9" s="15">
         <f t="shared" si="0"/>
-        <v>11.127000000000001</v>
+        <v>11.058999999999999</v>
       </c>
       <c r="H9" s="15">
         <f t="shared" si="1"/>
-        <v>7.7119999999999997</v>
+        <v>9.3149999999999995</v>
       </c>
       <c r="I9" s="16">
         <f t="shared" si="2"/>
-        <v>2.6224369549846807</v>
+        <v>2.6064105585670516</v>
       </c>
       <c r="J9" s="17"/>
     </row>
@@ -907,25 +907,25 @@
         <v>5309</v>
       </c>
       <c r="D10" s="7">
-        <v>10952</v>
+        <v>10884</v>
       </c>
       <c r="E10" s="7">
-        <v>5677</v>
+        <v>3859</v>
       </c>
       <c r="F10" s="7">
         <v>3547</v>
       </c>
       <c r="G10" s="8">
         <f t="shared" si="0"/>
-        <v>10.952</v>
+        <v>10.884</v>
       </c>
       <c r="H10" s="8">
         <f t="shared" si="1"/>
-        <v>5.6769999999999996</v>
+        <v>3.859</v>
       </c>
       <c r="I10" s="9">
         <f t="shared" si="2"/>
-        <v>3.0876797293487455</v>
+        <v>3.0685085988159009</v>
       </c>
       <c r="J10" s="10"/>
     </row>
@@ -940,25 +940,25 @@
         <v>3448</v>
       </c>
       <c r="D11" s="7">
-        <v>10508</v>
+        <v>10441</v>
       </c>
       <c r="E11" s="7">
-        <v>2119</v>
+        <v>2317</v>
       </c>
       <c r="F11" s="7">
         <v>1527</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>10.507999999999999</v>
+        <v>10.441000000000001</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>2.1190000000000002</v>
+        <v>2.3170000000000002</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>6.881466928618206</v>
+        <v>6.8375900458415195</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -967,31 +967,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="5">
-        <v>99.23</v>
+        <v>77.290000000000006</v>
       </c>
       <c r="C12" s="6">
-        <v>4809</v>
+        <v>4270</v>
       </c>
       <c r="D12" s="7">
-        <v>10455</v>
+        <v>10206</v>
       </c>
       <c r="E12" s="7">
-        <v>3476</v>
+        <v>3290</v>
       </c>
       <c r="F12" s="7">
-        <v>2842</v>
+        <v>2214</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="0"/>
-        <v>10.455</v>
+        <v>10.206</v>
       </c>
       <c r="H12" s="8">
         <f t="shared" si="1"/>
-        <v>3.476</v>
+        <v>3.29</v>
       </c>
       <c r="I12" s="9">
         <f t="shared" si="2"/>
-        <v>3.6787473610133707</v>
+        <v>4.6097560975609753</v>
       </c>
       <c r="J12" s="10"/>
     </row>
@@ -1000,97 +1000,97 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>77.290000000000006</v>
+        <v>99.23</v>
       </c>
       <c r="C13" s="6">
-        <v>4270</v>
+        <v>4809</v>
       </c>
       <c r="D13" s="7">
-        <v>10273</v>
+        <v>10192</v>
       </c>
       <c r="E13" s="7">
-        <v>5107</v>
+        <v>3674</v>
       </c>
       <c r="F13" s="7">
-        <v>2214</v>
+        <v>2842</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>10.273</v>
+        <v>10.192</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>5.1070000000000002</v>
+        <v>3.6739999999999999</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>4.6400180668473352</v>
+        <v>3.5862068965517242</v>
       </c>
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="5">
-        <v>98.26</v>
-      </c>
-      <c r="C14" s="6">
-        <v>4388</v>
-      </c>
-      <c r="D14" s="7">
-        <v>8900</v>
-      </c>
-      <c r="E14" s="7">
-        <v>4144</v>
-      </c>
-      <c r="F14" s="7">
-        <v>2039</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="0"/>
-        <v>8.9</v>
-      </c>
-      <c r="H14" s="8">
-        <f t="shared" si="1"/>
-        <v>4.1440000000000001</v>
-      </c>
-      <c r="I14" s="9">
-        <f t="shared" si="2"/>
-        <v>4.3648847474252088</v>
-      </c>
-      <c r="J14" s="10"/>
+      <c r="B14" s="19">
+        <v>106.47</v>
+      </c>
+      <c r="C14" s="20">
+        <v>4634</v>
+      </c>
+      <c r="D14" s="21">
+        <v>9060</v>
+      </c>
+      <c r="E14" s="21">
+        <v>4684</v>
+      </c>
+      <c r="F14" s="21">
+        <v>4379</v>
+      </c>
+      <c r="G14" s="22">
+        <f t="shared" si="0"/>
+        <v>9.06</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="1"/>
+        <v>4.6840000000000002</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="2"/>
+        <v>2.0689655172413794</v>
+      </c>
+      <c r="J14" s="24"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>135.58000000000001</v>
+        <v>98.26</v>
       </c>
       <c r="C15" s="6">
-        <v>4844</v>
+        <v>4388</v>
       </c>
       <c r="D15" s="7">
-        <v>7855</v>
+        <v>8833</v>
       </c>
       <c r="E15" s="7">
-        <v>1555</v>
+        <v>2326</v>
       </c>
       <c r="F15" s="7">
-        <v>1228</v>
+        <v>2039</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>7.8550000000000004</v>
+        <v>8.8330000000000002</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>1.5549999999999999</v>
+        <v>2.3260000000000001</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>6.3965798045602602</v>
+        <v>4.3320255026974008</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1105,25 +1105,25 @@
         <v>5776</v>
       </c>
       <c r="D16" s="7">
-        <v>7783</v>
+        <v>7716</v>
       </c>
       <c r="E16" s="7">
-        <v>2220</v>
+        <v>2328</v>
       </c>
       <c r="F16" s="7">
         <v>2045</v>
       </c>
       <c r="G16" s="8">
         <f t="shared" si="0"/>
-        <v>7.7830000000000004</v>
+        <v>7.7160000000000002</v>
       </c>
       <c r="H16" s="8">
         <f t="shared" si="1"/>
-        <v>2.2200000000000002</v>
+        <v>2.3279999999999998</v>
       </c>
       <c r="I16" s="9">
         <f t="shared" si="2"/>
-        <v>3.8058679706601466</v>
+        <v>3.7731051344743278</v>
       </c>
       <c r="J16" s="10"/>
     </row>
@@ -1138,289 +1138,289 @@
         <v>5633</v>
       </c>
       <c r="D17" s="14">
-        <v>7779</v>
+        <v>7712</v>
       </c>
       <c r="E17" s="14">
-        <v>4618</v>
+        <v>3864</v>
       </c>
       <c r="F17" s="14">
         <v>3546</v>
       </c>
       <c r="G17" s="15">
         <f t="shared" si="0"/>
-        <v>7.7789999999999999</v>
+        <v>7.7119999999999997</v>
       </c>
       <c r="H17" s="15">
         <f t="shared" si="1"/>
-        <v>4.6180000000000003</v>
+        <v>3.8639999999999999</v>
       </c>
       <c r="I17" s="16">
         <f t="shared" si="2"/>
-        <v>2.1937394247038915</v>
+        <v>2.1748448956570785</v>
       </c>
       <c r="J17" s="17"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="5">
-        <v>37.65</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2574</v>
-      </c>
-      <c r="D18" s="7">
-        <v>7666</v>
-      </c>
-      <c r="E18" s="7">
-        <v>5396</v>
-      </c>
-      <c r="F18" s="7">
-        <v>2446</v>
-      </c>
-      <c r="G18" s="8">
-        <f t="shared" si="0"/>
-        <v>7.6660000000000004</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" si="1"/>
-        <v>5.3959999999999999</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="2"/>
-        <v>3.1340964840556009</v>
-      </c>
-      <c r="J18" s="10"/>
+      <c r="B18" s="19">
+        <v>151.93</v>
+      </c>
+      <c r="C18" s="20">
+        <v>5346</v>
+      </c>
+      <c r="D18" s="21">
+        <v>7379</v>
+      </c>
+      <c r="E18" s="21">
+        <v>4168</v>
+      </c>
+      <c r="F18" s="21">
+        <v>2898</v>
+      </c>
+      <c r="G18" s="22">
+        <f t="shared" si="0"/>
+        <v>7.3789999999999996</v>
+      </c>
+      <c r="H18" s="22">
+        <f t="shared" si="1"/>
+        <v>4.1680000000000001</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="2"/>
+        <v>2.5462387853692201</v>
+      </c>
+      <c r="J18" s="24"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="12">
-        <v>151.93</v>
-      </c>
-      <c r="C19" s="13">
-        <v>5346</v>
-      </c>
-      <c r="D19" s="14">
-        <v>7433</v>
-      </c>
-      <c r="E19" s="14">
-        <v>4687</v>
-      </c>
-      <c r="F19" s="14">
-        <v>2898</v>
-      </c>
-      <c r="G19" s="15">
-        <f t="shared" si="0"/>
-        <v>7.4329999999999998</v>
-      </c>
-      <c r="H19" s="15">
-        <f t="shared" si="1"/>
-        <v>4.6870000000000003</v>
-      </c>
-      <c r="I19" s="16">
-        <f t="shared" si="2"/>
-        <v>2.5648723257418911</v>
-      </c>
-      <c r="J19" s="17"/>
+      <c r="B19" s="5">
+        <v>180.3</v>
+      </c>
+      <c r="C19" s="6">
+        <v>5857</v>
+      </c>
+      <c r="D19" s="7">
+        <v>6591</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2312</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1530</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>6.5910000000000002</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="1"/>
+        <v>2.3119999999999998</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="2"/>
+        <v>4.3078431372549018</v>
+      </c>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="19">
-        <v>106.47</v>
+        <v>75.97</v>
       </c>
       <c r="C20" s="20">
-        <v>4634</v>
+        <v>3658</v>
       </c>
       <c r="D20" s="21">
-        <v>7318</v>
+        <v>6289</v>
       </c>
       <c r="E20" s="21">
-        <v>4609</v>
+        <v>4058</v>
       </c>
       <c r="F20" s="21">
-        <v>4379</v>
+        <v>2908</v>
       </c>
       <c r="G20" s="22">
         <f t="shared" si="0"/>
-        <v>7.3179999999999996</v>
+        <v>6.2889999999999997</v>
       </c>
       <c r="H20" s="22">
         <f t="shared" si="1"/>
-        <v>4.609</v>
+        <v>4.0579999999999998</v>
       </c>
       <c r="I20" s="23">
         <f t="shared" si="2"/>
-        <v>1.6711577985841517</v>
+        <v>2.1626547455295735</v>
       </c>
       <c r="J20" s="24"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="12">
-        <v>75.97</v>
-      </c>
-      <c r="C21" s="13">
-        <v>3658</v>
-      </c>
-      <c r="D21" s="14">
-        <v>7265</v>
-      </c>
-      <c r="E21" s="14">
-        <v>5689</v>
-      </c>
-      <c r="F21" s="14">
-        <v>2908</v>
-      </c>
-      <c r="G21" s="15">
-        <f t="shared" si="0"/>
-        <v>7.2649999999999997</v>
-      </c>
-      <c r="H21" s="15">
-        <f t="shared" si="1"/>
-        <v>5.6890000000000001</v>
-      </c>
-      <c r="I21" s="16">
-        <f t="shared" si="2"/>
-        <v>2.4982806052269599</v>
-      </c>
-      <c r="J21" s="17"/>
+      <c r="B21" s="5">
+        <v>130.25</v>
+      </c>
+      <c r="C21" s="6">
+        <v>8274</v>
+      </c>
+      <c r="D21" s="7">
+        <v>5492</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2305</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1498</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="0"/>
+        <v>5.492</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="1"/>
+        <v>2.3050000000000002</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="2"/>
+        <v>3.6662216288384513</v>
+      </c>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="5">
+        <v>177.46</v>
+      </c>
+      <c r="C22" s="6">
+        <v>5465</v>
+      </c>
+      <c r="D22" s="7">
+        <v>5218</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1574</v>
+      </c>
+      <c r="F22" s="7">
+        <v>969</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="0"/>
+        <v>5.218</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="1"/>
+        <v>1.5740000000000001</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="2"/>
+        <v>5.3849329205366354</v>
+      </c>
+      <c r="J22" s="10"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="12">
         <v>37.700000000000003</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C23" s="13">
         <v>2565</v>
       </c>
-      <c r="D22" s="21">
-        <v>7193</v>
-      </c>
-      <c r="E22" s="21">
-        <v>5880</v>
-      </c>
-      <c r="F22" s="21">
+      <c r="D23" s="14">
+        <v>5032</v>
+      </c>
+      <c r="E23" s="14">
+        <v>4062</v>
+      </c>
+      <c r="F23" s="14">
         <v>2476</v>
       </c>
-      <c r="G22" s="22">
-        <f t="shared" si="0"/>
-        <v>7.1929999999999996</v>
-      </c>
-      <c r="H22" s="22">
-        <f t="shared" si="1"/>
-        <v>5.88</v>
-      </c>
-      <c r="I22" s="23">
-        <f t="shared" si="2"/>
-        <v>2.9050888529886914</v>
-      </c>
-      <c r="J22" s="24"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="5">
-        <v>130.25</v>
-      </c>
-      <c r="C23" s="6">
-        <v>8274</v>
-      </c>
-      <c r="D23" s="7">
-        <v>6587</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2107</v>
-      </c>
-      <c r="F23" s="7">
-        <v>1498</v>
-      </c>
-      <c r="G23" s="8">
-        <f t="shared" si="0"/>
-        <v>6.5869999999999997</v>
-      </c>
-      <c r="H23" s="8">
-        <f t="shared" si="1"/>
-        <v>2.1070000000000002</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="2"/>
-        <v>4.3971962616822431</v>
-      </c>
-      <c r="J23" s="10"/>
+      <c r="G23" s="15">
+        <f t="shared" si="0"/>
+        <v>5.032</v>
+      </c>
+      <c r="H23" s="15">
+        <f t="shared" si="1"/>
+        <v>4.0620000000000003</v>
+      </c>
+      <c r="I23" s="16">
+        <f t="shared" si="2"/>
+        <v>2.0323101777059773</v>
+      </c>
+      <c r="J23" s="17"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="5">
-        <v>180.3</v>
-      </c>
-      <c r="C24" s="6">
-        <v>5857</v>
-      </c>
-      <c r="D24" s="7">
-        <v>6393</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2114</v>
-      </c>
-      <c r="F24" s="7">
-        <v>1530</v>
-      </c>
-      <c r="G24" s="8">
-        <f t="shared" si="0"/>
-        <v>6.3929999999999998</v>
-      </c>
-      <c r="H24" s="8">
-        <f t="shared" si="1"/>
-        <v>2.1139999999999999</v>
-      </c>
-      <c r="I24" s="9">
-        <f t="shared" si="2"/>
-        <v>4.1784313725490199</v>
-      </c>
-      <c r="J24" s="10"/>
+      <c r="B24" s="19">
+        <v>37.65</v>
+      </c>
+      <c r="C24" s="20">
+        <v>2574</v>
+      </c>
+      <c r="D24" s="21">
+        <v>4904</v>
+      </c>
+      <c r="E24" s="21">
+        <v>3579</v>
+      </c>
+      <c r="F24" s="21">
+        <v>2446</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="0"/>
+        <v>4.9039999999999999</v>
+      </c>
+      <c r="H24" s="22">
+        <f t="shared" si="1"/>
+        <v>3.5790000000000002</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="2"/>
+        <v>2.0049059689288633</v>
+      </c>
+      <c r="J24" s="24"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>78.38</v>
+        <v>135.58000000000001</v>
       </c>
       <c r="C25" s="6">
-        <v>4052</v>
+        <v>4844</v>
       </c>
       <c r="D25" s="7">
-        <v>6191</v>
+        <v>4538</v>
       </c>
       <c r="E25" s="7">
-        <v>1003</v>
+        <v>1584</v>
       </c>
       <c r="F25" s="7">
-        <v>767</v>
+        <v>1228</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>6.1909999999999998</v>
+        <v>4.5380000000000003</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>1.0029999999999999</v>
+        <v>1.5840000000000001</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>8.0717079530638856</v>
+        <v>3.6954397394136809</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1429,31 +1429,31 @@
         <v>33</v>
       </c>
       <c r="B26" s="5">
-        <v>156.94</v>
+        <v>78.38</v>
       </c>
       <c r="C26" s="6">
-        <v>5252</v>
+        <v>4052</v>
       </c>
       <c r="D26" s="7">
-        <v>5827</v>
+        <v>4374</v>
       </c>
       <c r="E26" s="7">
-        <v>873</v>
+        <v>1048</v>
       </c>
       <c r="F26" s="7">
-        <v>567</v>
+        <v>767</v>
       </c>
       <c r="G26" s="8">
         <f t="shared" si="0"/>
-        <v>5.827</v>
+        <v>4.3739999999999997</v>
       </c>
       <c r="H26" s="8">
         <f t="shared" si="1"/>
-        <v>0.873</v>
+        <v>1.048</v>
       </c>
       <c r="I26" s="9">
         <f t="shared" si="2"/>
-        <v>10.276895943562611</v>
+        <v>5.7027379400260756</v>
       </c>
       <c r="J26" s="10"/>
     </row>
@@ -1462,31 +1462,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>177.46</v>
+        <v>156.94</v>
       </c>
       <c r="C27" s="6">
-        <v>5465</v>
+        <v>5252</v>
       </c>
       <c r="D27" s="7">
-        <v>5189</v>
+        <v>4009</v>
       </c>
       <c r="E27" s="7">
-        <v>1545</v>
+        <v>826</v>
       </c>
       <c r="F27" s="7">
-        <v>969</v>
+        <v>567</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>5.1890000000000001</v>
+        <v>4.0090000000000003</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>1.5449999999999999</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>5.3550051599587203</v>
+        <v>7.0705467372134043</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1501,25 +1501,25 @@
         <v>4418</v>
       </c>
       <c r="D28" s="7">
-        <v>4849</v>
+        <v>3769</v>
       </c>
       <c r="E28" s="7">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F28" s="7">
         <v>546</v>
       </c>
       <c r="G28" s="8">
         <f t="shared" si="0"/>
-        <v>4.8490000000000002</v>
+        <v>3.7690000000000001</v>
       </c>
       <c r="H28" s="8">
         <f t="shared" si="1"/>
-        <v>0.56299999999999994</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I28" s="9">
         <f t="shared" si="2"/>
-        <v>8.8809523809523814</v>
+        <v>6.9029304029304033</v>
       </c>
       <c r="J28" s="10"/>
     </row>
@@ -1534,7 +1534,7 @@
         <v>5481</v>
       </c>
       <c r="D29" s="7">
-        <v>4593</v>
+        <v>3498</v>
       </c>
       <c r="E29" s="7">
         <v>292</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>4.593</v>
+        <v>3.4980000000000002</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>15.783505154639176</v>
+        <v>12.020618556701031</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1567,25 +1567,25 @@
         <v>4022</v>
       </c>
       <c r="D30" s="7">
-        <v>3335</v>
+        <v>2704</v>
       </c>
       <c r="E30" s="7">
-        <v>1027</v>
+        <v>1074</v>
       </c>
       <c r="F30" s="7">
         <v>473</v>
       </c>
       <c r="G30" s="8">
         <f t="shared" si="0"/>
-        <v>3.335</v>
+        <v>2.7040000000000002</v>
       </c>
       <c r="H30" s="8">
         <f t="shared" si="1"/>
-        <v>1.0269999999999999</v>
+        <v>1.0740000000000001</v>
       </c>
       <c r="I30" s="9">
         <f t="shared" si="2"/>
-        <v>7.0507399577167016</v>
+        <v>5.7167019027484143</v>
       </c>
       <c r="J30" s="10"/>
     </row>
@@ -1600,25 +1600,25 @@
         <v>3752</v>
       </c>
       <c r="D31" s="7">
-        <v>3084</v>
+        <v>2049</v>
       </c>
       <c r="E31" s="7">
-        <v>610</v>
+        <v>119</v>
       </c>
       <c r="F31" s="7">
         <v>121</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>3.0840000000000001</v>
+        <v>2.0489999999999999</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>0.61</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>25.487603305785125</v>
+        <v>16.93388429752066</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1633,7 +1633,7 @@
         <v>4288</v>
       </c>
       <c r="D32" s="7">
-        <v>2597</v>
+        <v>1523</v>
       </c>
       <c r="E32" s="7">
         <v>142</v>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="G32" s="8">
         <f t="shared" si="0"/>
-        <v>2.597</v>
+        <v>1.5229999999999999</v>
       </c>
       <c r="H32" s="8">
         <f t="shared" si="1"/>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="I32" s="9">
         <f t="shared" si="2"/>
-        <v>18.288732394366196</v>
+        <v>10.725352112676056</v>
       </c>
       <c r="J32" s="10"/>
     </row>
@@ -1661,19 +1661,19 @@
       </c>
       <c r="B34" s="26">
         <f>SUM(B5:B32)</f>
-        <v>2958.4700000000007</v>
+        <v>2958.4700000000003</v>
       </c>
       <c r="D34" s="27">
         <f>MAX(D5:D32)</f>
-        <v>13492</v>
+        <v>13406</v>
       </c>
       <c r="G34" s="28">
         <f>IFERROR(MAX(G5:G32),"")</f>
-        <v>13.492000000000001</v>
+        <v>13.406000000000001</v>
       </c>
       <c r="I34" s="29">
         <f>IFERROR(AVERAGE(I5:I32),"")</f>
-        <v>6.2840808987375851</v>
+        <v>5.0528342641278305</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9F7663-39DD-48D4-ADD7-A10282A245D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3020CF9F-678D-4422-B0FA-DCFCE030056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
   <si>
     <t>FAZENDA MATO GROSSO — distância dos talhões até a sede</t>
   </si>
@@ -72,88 +72,97 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-13</t>
+  </si>
+  <si>
+    <t>T-10</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-11</t>
+  </si>
+  <si>
     <t>T-03</t>
   </si>
   <si>
     <t>T-07</t>
   </si>
   <si>
-    <t>T-04</t>
+    <t>T-11A</t>
+  </si>
+  <si>
+    <t>T-12</t>
+  </si>
+  <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>T-17</t>
   </si>
   <si>
     <t>T-08</t>
   </si>
   <si>
+    <t>T-15</t>
+  </si>
+  <si>
+    <t>T-16</t>
+  </si>
+  <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-21</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-21R</t>
+  </si>
+  <si>
+    <t>A-01</t>
+  </si>
+  <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-20</t>
+  </si>
+  <si>
+    <t>T-19</t>
+  </si>
+  <si>
+    <t>T-10A</t>
+  </si>
+  <si>
+    <t>P-02</t>
+  </si>
+  <si>
+    <t>T-18</t>
+  </si>
+  <si>
+    <t>R-08</t>
+  </si>
+  <si>
     <t>P-26</t>
   </si>
   <si>
-    <t>T-12</t>
-  </si>
-  <si>
-    <t>T-10A</t>
-  </si>
-  <si>
-    <t>T-11A</t>
-  </si>
-  <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>T-17</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-15</t>
-  </si>
-  <si>
-    <t>T-16</t>
-  </si>
-  <si>
-    <t>T-01</t>
-  </si>
-  <si>
-    <t>T-06</t>
-  </si>
-  <si>
-    <t>T-21</t>
-  </si>
-  <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-19</t>
-  </si>
-  <si>
-    <t>T-21R</t>
-  </si>
-  <si>
-    <t>A-01</t>
-  </si>
-  <si>
-    <t>T-20</t>
-  </si>
-  <si>
-    <t>P-02</t>
-  </si>
-  <si>
-    <t>T-10</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>T-18</t>
-  </si>
-  <si>
-    <t>R-08</t>
-  </si>
-  <si>
-    <t>T-13</t>
+    <t>sem acesso</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>sem estrada até este talhão</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -232,7 +241,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,6 +284,17 @@
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -333,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -361,13 +381,21 @@
     <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -736,31 +764,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>124.45</v>
+        <v>182.48</v>
       </c>
       <c r="C5" s="6">
-        <v>4845</v>
+        <v>5481</v>
       </c>
       <c r="D5" s="7">
-        <v>13406</v>
+        <v>14839</v>
       </c>
       <c r="E5" s="7">
-        <v>6252</v>
+        <v>13289</v>
       </c>
       <c r="F5" s="7">
-        <v>2795</v>
+        <v>291</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:G32" si="0">D5/1000</f>
-        <v>13.406000000000001</v>
+        <f t="shared" ref="G5:G31" si="0">D5/1000</f>
+        <v>14.839</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" ref="H5:H32" si="1">E5/1000</f>
-        <v>6.2519999999999998</v>
+        <f t="shared" ref="H5:H31" si="1">E5/1000</f>
+        <v>13.289</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I5:I32" si="2">IFERROR(D5/F5,"")</f>
-        <v>4.7964221824686941</v>
+        <f t="shared" ref="I5:I31" si="2">IFERROR(D5/F5,"")</f>
+        <v>50.993127147766323</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -769,31 +797,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="5">
-        <v>133.59</v>
+        <v>42.11</v>
       </c>
       <c r="C6" s="6">
-        <v>4784</v>
+        <v>4288</v>
       </c>
       <c r="D6" s="7">
-        <v>13406</v>
+        <v>14813</v>
       </c>
       <c r="E6" s="7">
-        <v>3445</v>
+        <v>13315</v>
       </c>
       <c r="F6" s="7">
-        <v>2279</v>
+        <v>142</v>
       </c>
       <c r="G6" s="8">
         <f t="shared" si="0"/>
-        <v>13.406000000000001</v>
+        <v>14.813000000000001</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="1"/>
-        <v>3.4449999999999998</v>
+        <v>13.315</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="2"/>
-        <v>5.882404563405002</v>
+        <v>104.3169014084507</v>
       </c>
       <c r="J6" s="10"/>
     </row>
@@ -802,31 +830,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>69.11</v>
+        <v>156.94</v>
       </c>
       <c r="C7" s="6">
-        <v>3352</v>
+        <v>5252</v>
       </c>
       <c r="D7" s="7">
-        <v>13229</v>
+        <v>13341</v>
       </c>
       <c r="E7" s="7">
-        <v>11171</v>
+        <v>11763</v>
       </c>
       <c r="F7" s="7">
-        <v>4020</v>
+        <v>567</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>13.228999999999999</v>
+        <v>13.340999999999999</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>11.170999999999999</v>
+        <v>11.763</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>3.2907960199004975</v>
+        <v>23.529100529100528</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -835,31 +863,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="5">
-        <v>94.59</v>
+        <v>103.71</v>
       </c>
       <c r="C8" s="6">
-        <v>3957</v>
+        <v>4418</v>
       </c>
       <c r="D8" s="7">
-        <v>13228</v>
+        <v>13341</v>
       </c>
       <c r="E8" s="7">
-        <v>8942</v>
+        <v>11763</v>
       </c>
       <c r="F8" s="7">
-        <v>3696</v>
+        <v>546</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="0"/>
-        <v>13.228</v>
+        <v>13.340999999999999</v>
       </c>
       <c r="H8" s="8">
         <f t="shared" si="1"/>
-        <v>8.9420000000000002</v>
+        <v>11.763</v>
       </c>
       <c r="I8" s="9">
         <f t="shared" si="2"/>
-        <v>3.579004329004329</v>
+        <v>24.434065934065934</v>
       </c>
       <c r="J8" s="10"/>
     </row>
@@ -868,31 +896,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="12">
-        <v>38.369999999999997</v>
+        <v>69.11</v>
       </c>
       <c r="C9" s="13">
-        <v>2500</v>
+        <v>3352</v>
       </c>
       <c r="D9" s="14">
-        <v>11059</v>
+        <v>11965</v>
       </c>
       <c r="E9" s="14">
-        <v>9315</v>
+        <v>11137</v>
       </c>
       <c r="F9" s="14">
-        <v>4243</v>
+        <v>4020</v>
       </c>
       <c r="G9" s="15">
         <f t="shared" si="0"/>
-        <v>11.058999999999999</v>
+        <v>11.965</v>
       </c>
       <c r="H9" s="15">
         <f t="shared" si="1"/>
-        <v>9.3149999999999995</v>
+        <v>11.137</v>
       </c>
       <c r="I9" s="16">
         <f t="shared" si="2"/>
-        <v>2.6064105585670516</v>
+        <v>2.9763681592039801</v>
       </c>
       <c r="J9" s="17"/>
     </row>
@@ -901,31 +929,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="5">
-        <v>123.95</v>
+        <v>98.26</v>
       </c>
       <c r="C10" s="6">
-        <v>5309</v>
+        <v>4388</v>
       </c>
       <c r="D10" s="7">
-        <v>10884</v>
+        <v>11815</v>
       </c>
       <c r="E10" s="7">
-        <v>3859</v>
+        <v>10255</v>
       </c>
       <c r="F10" s="7">
-        <v>3547</v>
+        <v>2039</v>
       </c>
       <c r="G10" s="8">
         <f t="shared" si="0"/>
-        <v>10.884</v>
+        <v>11.815</v>
       </c>
       <c r="H10" s="8">
         <f t="shared" si="1"/>
-        <v>3.859</v>
+        <v>10.255000000000001</v>
       </c>
       <c r="I10" s="9">
         <f t="shared" si="2"/>
-        <v>3.0685085988159009</v>
+        <v>5.7945071113290831</v>
       </c>
       <c r="J10" s="10"/>
     </row>
@@ -934,31 +962,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>25.3</v>
+        <v>124.45</v>
       </c>
       <c r="C11" s="6">
-        <v>3448</v>
+        <v>4845</v>
       </c>
       <c r="D11" s="7">
-        <v>10441</v>
+        <v>11192</v>
       </c>
       <c r="E11" s="7">
-        <v>2317</v>
+        <v>9579</v>
       </c>
       <c r="F11" s="7">
-        <v>1527</v>
+        <v>2795</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>10.441000000000001</v>
+        <v>11.192</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>2.3170000000000002</v>
+        <v>9.5790000000000006</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>6.8375900458415195</v>
+        <v>4.0042933810375674</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -967,31 +995,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="5">
-        <v>77.290000000000006</v>
+        <v>133.59</v>
       </c>
       <c r="C12" s="6">
-        <v>4270</v>
+        <v>4784</v>
       </c>
       <c r="D12" s="7">
-        <v>10206</v>
+        <v>10433</v>
       </c>
       <c r="E12" s="7">
-        <v>3290</v>
+        <v>8897</v>
       </c>
       <c r="F12" s="7">
-        <v>2214</v>
+        <v>2279</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="0"/>
-        <v>10.206</v>
+        <v>10.433</v>
       </c>
       <c r="H12" s="8">
         <f t="shared" si="1"/>
-        <v>3.29</v>
+        <v>8.8970000000000002</v>
       </c>
       <c r="I12" s="9">
         <f t="shared" si="2"/>
-        <v>4.6097560975609753</v>
+        <v>4.5778850372970599</v>
       </c>
       <c r="J12" s="10"/>
     </row>
@@ -1000,31 +1028,31 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>99.23</v>
+        <v>77.290000000000006</v>
       </c>
       <c r="C13" s="6">
-        <v>4809</v>
+        <v>4270</v>
       </c>
       <c r="D13" s="7">
-        <v>10192</v>
+        <v>10433</v>
       </c>
       <c r="E13" s="7">
-        <v>3674</v>
+        <v>7965</v>
       </c>
       <c r="F13" s="7">
-        <v>2842</v>
+        <v>2214</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>10.192</v>
+        <v>10.433</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>3.6739999999999999</v>
+        <v>7.9649999999999999</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>3.5862068965517242</v>
+        <v>4.7122854561878951</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1033,31 +1061,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="19">
-        <v>106.47</v>
+        <v>123.95</v>
       </c>
       <c r="C14" s="20">
-        <v>4634</v>
+        <v>5309</v>
       </c>
       <c r="D14" s="21">
-        <v>9060</v>
+        <v>10305</v>
       </c>
       <c r="E14" s="21">
-        <v>4684</v>
+        <v>8696</v>
       </c>
       <c r="F14" s="21">
-        <v>4379</v>
+        <v>3547</v>
       </c>
       <c r="G14" s="22">
         <f t="shared" si="0"/>
-        <v>9.06</v>
+        <v>10.305</v>
       </c>
       <c r="H14" s="22">
         <f t="shared" si="1"/>
-        <v>4.6840000000000002</v>
+        <v>8.6959999999999997</v>
       </c>
       <c r="I14" s="23">
         <f t="shared" si="2"/>
-        <v>2.0689655172413794</v>
+        <v>2.9052720608965323</v>
       </c>
       <c r="J14" s="24"/>
     </row>
@@ -1066,262 +1094,262 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>98.26</v>
+        <v>99.23</v>
       </c>
       <c r="C15" s="6">
-        <v>4388</v>
+        <v>4809</v>
       </c>
       <c r="D15" s="7">
-        <v>8833</v>
+        <v>9640</v>
       </c>
       <c r="E15" s="7">
-        <v>2326</v>
+        <v>7819</v>
       </c>
       <c r="F15" s="7">
-        <v>2039</v>
+        <v>2842</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>8.8330000000000002</v>
+        <v>9.64</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>2.3260000000000001</v>
+        <v>7.819</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>4.3320255026974008</v>
+        <v>3.3919774806474314</v>
       </c>
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="5">
-        <v>200.37</v>
-      </c>
-      <c r="C16" s="6">
-        <v>5776</v>
-      </c>
-      <c r="D16" s="7">
-        <v>7716</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2328</v>
-      </c>
-      <c r="F16" s="7">
-        <v>2045</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" si="0"/>
-        <v>7.7160000000000002</v>
-      </c>
-      <c r="H16" s="8">
-        <f t="shared" si="1"/>
-        <v>2.3279999999999998</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="2"/>
-        <v>3.7731051344743278</v>
-      </c>
-      <c r="J16" s="10"/>
+      <c r="B16" s="19">
+        <v>106.47</v>
+      </c>
+      <c r="C16" s="20">
+        <v>4634</v>
+      </c>
+      <c r="D16" s="21">
+        <v>9450</v>
+      </c>
+      <c r="E16" s="21">
+        <v>7892</v>
+      </c>
+      <c r="F16" s="21">
+        <v>4379</v>
+      </c>
+      <c r="G16" s="22">
+        <f t="shared" si="0"/>
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="H16" s="22">
+        <f t="shared" si="1"/>
+        <v>7.8920000000000003</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="2"/>
+        <v>2.1580269467915048</v>
+      </c>
+      <c r="J16" s="24"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="12">
+        <v>94.59</v>
+      </c>
+      <c r="C17" s="13">
+        <v>3957</v>
+      </c>
+      <c r="D17" s="14">
+        <v>8939</v>
+      </c>
+      <c r="E17" s="14">
+        <v>8923</v>
+      </c>
+      <c r="F17" s="14">
+        <v>3696</v>
+      </c>
+      <c r="G17" s="15">
+        <f t="shared" si="0"/>
+        <v>8.9390000000000001</v>
+      </c>
+      <c r="H17" s="15">
+        <f t="shared" si="1"/>
+        <v>8.923</v>
+      </c>
+      <c r="I17" s="16">
+        <f t="shared" si="2"/>
+        <v>2.418560606060606</v>
+      </c>
+      <c r="J17" s="17"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="5">
+        <v>200.37</v>
+      </c>
+      <c r="C18" s="6">
+        <v>5776</v>
+      </c>
+      <c r="D18" s="7">
+        <v>7739</v>
+      </c>
+      <c r="E18" s="7">
+        <v>6203</v>
+      </c>
+      <c r="F18" s="7">
+        <v>2045</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="0"/>
+        <v>7.7389999999999999</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="1"/>
+        <v>6.2030000000000003</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="2"/>
+        <v>3.7843520782396087</v>
+      </c>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="12">
         <v>151.26</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C19" s="13">
         <v>5633</v>
       </c>
-      <c r="D17" s="14">
-        <v>7712</v>
-      </c>
-      <c r="E17" s="14">
-        <v>3864</v>
-      </c>
-      <c r="F17" s="14">
+      <c r="D19" s="14">
+        <v>7739</v>
+      </c>
+      <c r="E19" s="14">
+        <v>5605</v>
+      </c>
+      <c r="F19" s="14">
         <v>3546</v>
       </c>
-      <c r="G17" s="15">
-        <f t="shared" si="0"/>
-        <v>7.7119999999999997</v>
-      </c>
-      <c r="H17" s="15">
-        <f t="shared" si="1"/>
-        <v>3.8639999999999999</v>
-      </c>
-      <c r="I17" s="16">
-        <f t="shared" si="2"/>
-        <v>2.1748448956570785</v>
-      </c>
-      <c r="J17" s="17"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="19">
-        <v>151.93</v>
-      </c>
-      <c r="C18" s="20">
-        <v>5346</v>
-      </c>
-      <c r="D18" s="21">
-        <v>7379</v>
-      </c>
-      <c r="E18" s="21">
-        <v>4168</v>
-      </c>
-      <c r="F18" s="21">
-        <v>2898</v>
-      </c>
-      <c r="G18" s="22">
-        <f t="shared" si="0"/>
-        <v>7.3789999999999996</v>
-      </c>
-      <c r="H18" s="22">
-        <f t="shared" si="1"/>
-        <v>4.1680000000000001</v>
-      </c>
-      <c r="I18" s="23">
-        <f t="shared" si="2"/>
-        <v>2.5462387853692201</v>
-      </c>
-      <c r="J18" s="24"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="5">
-        <v>180.3</v>
-      </c>
-      <c r="C19" s="6">
-        <v>5857</v>
-      </c>
-      <c r="D19" s="7">
-        <v>6591</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2312</v>
-      </c>
-      <c r="F19" s="7">
-        <v>1530</v>
-      </c>
-      <c r="G19" s="8">
-        <f t="shared" si="0"/>
-        <v>6.5910000000000002</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="1"/>
-        <v>2.3119999999999998</v>
-      </c>
-      <c r="I19" s="9">
-        <f t="shared" si="2"/>
-        <v>4.3078431372549018</v>
-      </c>
-      <c r="J19" s="10"/>
+      <c r="G19" s="15">
+        <f t="shared" si="0"/>
+        <v>7.7389999999999999</v>
+      </c>
+      <c r="H19" s="15">
+        <f t="shared" si="1"/>
+        <v>5.6050000000000004</v>
+      </c>
+      <c r="I19" s="16">
+        <f t="shared" si="2"/>
+        <v>2.1824591088550478</v>
+      </c>
+      <c r="J19" s="17"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="19">
+        <v>151.93</v>
+      </c>
+      <c r="C20" s="20">
+        <v>5346</v>
+      </c>
+      <c r="D20" s="21">
+        <v>6963</v>
+      </c>
+      <c r="E20" s="21">
+        <v>4105</v>
+      </c>
+      <c r="F20" s="21">
+        <v>2898</v>
+      </c>
+      <c r="G20" s="22">
+        <f t="shared" si="0"/>
+        <v>6.9630000000000001</v>
+      </c>
+      <c r="H20" s="22">
+        <f t="shared" si="1"/>
+        <v>4.1050000000000004</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="2"/>
+        <v>2.4026915113871636</v>
+      </c>
+      <c r="J20" s="24"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="12">
         <v>75.97</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C21" s="13">
         <v>3658</v>
       </c>
-      <c r="D20" s="21">
-        <v>6289</v>
-      </c>
-      <c r="E20" s="21">
-        <v>4058</v>
-      </c>
-      <c r="F20" s="21">
+      <c r="D21" s="14">
+        <v>6254</v>
+      </c>
+      <c r="E21" s="14">
+        <v>4419</v>
+      </c>
+      <c r="F21" s="14">
         <v>2908</v>
       </c>
-      <c r="G20" s="22">
-        <f t="shared" si="0"/>
-        <v>6.2889999999999997</v>
-      </c>
-      <c r="H20" s="22">
-        <f t="shared" si="1"/>
-        <v>4.0579999999999998</v>
-      </c>
-      <c r="I20" s="23">
-        <f t="shared" si="2"/>
-        <v>2.1626547455295735</v>
-      </c>
-      <c r="J20" s="24"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="5">
-        <v>130.25</v>
-      </c>
-      <c r="C21" s="6">
-        <v>8274</v>
-      </c>
-      <c r="D21" s="7">
-        <v>5492</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2305</v>
-      </c>
-      <c r="F21" s="7">
-        <v>1498</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="0"/>
-        <v>5.492</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="1"/>
-        <v>2.3050000000000002</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="2"/>
-        <v>3.6662216288384513</v>
-      </c>
-      <c r="J21" s="10"/>
+      <c r="G21" s="15">
+        <f t="shared" si="0"/>
+        <v>6.2539999999999996</v>
+      </c>
+      <c r="H21" s="15">
+        <f t="shared" si="1"/>
+        <v>4.4189999999999996</v>
+      </c>
+      <c r="I21" s="16">
+        <f t="shared" si="2"/>
+        <v>2.1506189821182944</v>
+      </c>
+      <c r="J21" s="17"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="5">
-        <v>177.46</v>
+        <v>180.3</v>
       </c>
       <c r="C22" s="6">
-        <v>5465</v>
+        <v>5857</v>
       </c>
       <c r="D22" s="7">
-        <v>5218</v>
+        <v>6045</v>
       </c>
       <c r="E22" s="7">
-        <v>1574</v>
+        <v>2269</v>
       </c>
       <c r="F22" s="7">
-        <v>969</v>
+        <v>1530</v>
       </c>
       <c r="G22" s="8">
         <f t="shared" si="0"/>
-        <v>5.218</v>
+        <v>6.0449999999999999</v>
       </c>
       <c r="H22" s="8">
         <f t="shared" si="1"/>
-        <v>1.5740000000000001</v>
+        <v>2.2690000000000001</v>
       </c>
       <c r="I22" s="9">
         <f t="shared" si="2"/>
-        <v>5.3849329205366354</v>
+        <v>3.9509803921568629</v>
       </c>
       <c r="J22" s="10"/>
     </row>
@@ -1336,25 +1364,25 @@
         <v>2565</v>
       </c>
       <c r="D23" s="14">
-        <v>5032</v>
+        <v>4528</v>
       </c>
       <c r="E23" s="14">
-        <v>4062</v>
+        <v>4097</v>
       </c>
       <c r="F23" s="14">
         <v>2476</v>
       </c>
       <c r="G23" s="15">
         <f t="shared" si="0"/>
-        <v>5.032</v>
+        <v>4.5279999999999996</v>
       </c>
       <c r="H23" s="15">
         <f t="shared" si="1"/>
-        <v>4.0620000000000003</v>
+        <v>4.0970000000000004</v>
       </c>
       <c r="I23" s="16">
         <f t="shared" si="2"/>
-        <v>2.0323101777059773</v>
+        <v>1.8287560581583198</v>
       </c>
       <c r="J23" s="17"/>
     </row>
@@ -1369,91 +1397,91 @@
         <v>2574</v>
       </c>
       <c r="D24" s="21">
-        <v>4904</v>
+        <v>4485</v>
       </c>
       <c r="E24" s="21">
-        <v>3579</v>
+        <v>4061</v>
       </c>
       <c r="F24" s="21">
         <v>2446</v>
       </c>
       <c r="G24" s="22">
         <f t="shared" si="0"/>
-        <v>4.9039999999999999</v>
+        <v>4.4850000000000003</v>
       </c>
       <c r="H24" s="22">
         <f t="shared" si="1"/>
-        <v>3.5790000000000002</v>
+        <v>4.0609999999999999</v>
       </c>
       <c r="I24" s="23">
         <f t="shared" si="2"/>
-        <v>2.0049059689288633</v>
+        <v>1.8336058871627146</v>
       </c>
       <c r="J24" s="24"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="5">
-        <v>135.58000000000001</v>
-      </c>
-      <c r="C25" s="6">
-        <v>4844</v>
-      </c>
-      <c r="D25" s="7">
-        <v>4538</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1584</v>
-      </c>
-      <c r="F25" s="7">
-        <v>1228</v>
-      </c>
-      <c r="G25" s="8">
-        <f t="shared" si="0"/>
-        <v>4.5380000000000003</v>
-      </c>
-      <c r="H25" s="8">
-        <f t="shared" si="1"/>
-        <v>1.5840000000000001</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="2"/>
-        <v>3.6954397394136809</v>
-      </c>
-      <c r="J25" s="10"/>
+      <c r="B25" s="12">
+        <v>130.25</v>
+      </c>
+      <c r="C25" s="13">
+        <v>8274</v>
+      </c>
+      <c r="D25" s="14">
+        <v>4155</v>
+      </c>
+      <c r="E25" s="14">
+        <v>2730</v>
+      </c>
+      <c r="F25" s="14">
+        <v>1498</v>
+      </c>
+      <c r="G25" s="15">
+        <f t="shared" si="0"/>
+        <v>4.1550000000000002</v>
+      </c>
+      <c r="H25" s="15">
+        <f t="shared" si="1"/>
+        <v>2.73</v>
+      </c>
+      <c r="I25" s="16">
+        <f t="shared" si="2"/>
+        <v>2.7736982643524701</v>
+      </c>
+      <c r="J25" s="17"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="5">
-        <v>78.38</v>
+        <v>135.58000000000001</v>
       </c>
       <c r="C26" s="6">
-        <v>4052</v>
+        <v>4844</v>
       </c>
       <c r="D26" s="7">
-        <v>4374</v>
+        <v>4097</v>
       </c>
       <c r="E26" s="7">
-        <v>1048</v>
+        <v>1555</v>
       </c>
       <c r="F26" s="7">
-        <v>767</v>
+        <v>1228</v>
       </c>
       <c r="G26" s="8">
         <f t="shared" si="0"/>
-        <v>4.3739999999999997</v>
+        <v>4.0970000000000004</v>
       </c>
       <c r="H26" s="8">
         <f t="shared" si="1"/>
-        <v>1.048</v>
+        <v>1.5549999999999999</v>
       </c>
       <c r="I26" s="9">
         <f t="shared" si="2"/>
-        <v>5.7027379400260756</v>
+        <v>3.3363192182410422</v>
       </c>
       <c r="J26" s="10"/>
     </row>
@@ -1462,99 +1490,99 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>156.94</v>
+        <v>177.46</v>
       </c>
       <c r="C27" s="6">
-        <v>5252</v>
+        <v>5465</v>
       </c>
       <c r="D27" s="7">
-        <v>4009</v>
+        <v>4094</v>
       </c>
       <c r="E27" s="7">
-        <v>826</v>
+        <v>1555</v>
       </c>
       <c r="F27" s="7">
-        <v>567</v>
+        <v>969</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>4.0090000000000003</v>
+        <v>4.0940000000000003</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>0.82599999999999996</v>
+        <v>1.5549999999999999</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>7.0705467372134043</v>
+        <v>4.2249742002063986</v>
       </c>
       <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="5">
-        <v>103.71</v>
-      </c>
-      <c r="C28" s="6">
-        <v>4418</v>
-      </c>
-      <c r="D28" s="7">
-        <v>3769</v>
-      </c>
-      <c r="E28" s="7">
-        <v>560</v>
-      </c>
-      <c r="F28" s="7">
-        <v>546</v>
-      </c>
-      <c r="G28" s="8">
-        <f t="shared" si="0"/>
-        <v>3.7690000000000001</v>
-      </c>
-      <c r="H28" s="8">
-        <f t="shared" si="1"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" si="2"/>
-        <v>6.9029304029304033</v>
-      </c>
-      <c r="J28" s="10"/>
+      <c r="B28" s="19">
+        <v>25.3</v>
+      </c>
+      <c r="C28" s="20">
+        <v>3448</v>
+      </c>
+      <c r="D28" s="21">
+        <v>2326</v>
+      </c>
+      <c r="E28" s="21">
+        <v>2269</v>
+      </c>
+      <c r="F28" s="21">
+        <v>1527</v>
+      </c>
+      <c r="G28" s="22">
+        <f t="shared" si="0"/>
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="H28" s="22">
+        <f t="shared" si="1"/>
+        <v>2.2690000000000001</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="2"/>
+        <v>1.5232481990831697</v>
+      </c>
+      <c r="J28" s="24"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="5">
-        <v>182.48</v>
-      </c>
-      <c r="C29" s="6">
-        <v>5481</v>
-      </c>
-      <c r="D29" s="7">
-        <v>3498</v>
-      </c>
-      <c r="E29" s="7">
-        <v>292</v>
-      </c>
-      <c r="F29" s="7">
-        <v>291</v>
-      </c>
-      <c r="G29" s="8">
-        <f t="shared" si="0"/>
-        <v>3.4980000000000002</v>
-      </c>
-      <c r="H29" s="8">
-        <f t="shared" si="1"/>
-        <v>0.29199999999999998</v>
-      </c>
-      <c r="I29" s="9">
-        <f t="shared" si="2"/>
-        <v>12.020618556701031</v>
-      </c>
-      <c r="J29" s="10"/>
+      <c r="B29" s="12">
+        <v>78.38</v>
+      </c>
+      <c r="C29" s="13">
+        <v>4052</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1584</v>
+      </c>
+      <c r="E29" s="14">
+        <v>994</v>
+      </c>
+      <c r="F29" s="14">
+        <v>767</v>
+      </c>
+      <c r="G29" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5840000000000001</v>
+      </c>
+      <c r="H29" s="15">
+        <f t="shared" si="1"/>
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="I29" s="16">
+        <f t="shared" si="2"/>
+        <v>2.0651890482398958</v>
+      </c>
+      <c r="J29" s="17"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
@@ -1567,25 +1595,25 @@
         <v>4022</v>
       </c>
       <c r="D30" s="7">
-        <v>2704</v>
+        <v>1584</v>
       </c>
       <c r="E30" s="7">
-        <v>1074</v>
+        <v>1020</v>
       </c>
       <c r="F30" s="7">
         <v>473</v>
       </c>
       <c r="G30" s="8">
         <f t="shared" si="0"/>
-        <v>2.7040000000000002</v>
+        <v>1.5840000000000001</v>
       </c>
       <c r="H30" s="8">
         <f t="shared" si="1"/>
-        <v>1.0740000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="I30" s="9">
         <f t="shared" si="2"/>
-        <v>5.7167019027484143</v>
+        <v>3.3488372093023258</v>
       </c>
       <c r="J30" s="10"/>
     </row>
@@ -1600,7 +1628,7 @@
         <v>3752</v>
       </c>
       <c r="D31" s="7">
-        <v>2049</v>
+        <v>1100</v>
       </c>
       <c r="E31" s="7">
         <v>119</v>
@@ -1610,7 +1638,7 @@
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>2.0489999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
@@ -1618,7 +1646,7 @@
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>16.93388429752066</v>
+        <v>9.0909090909090917</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1627,58 +1655,57 @@
         <v>39</v>
       </c>
       <c r="B32" s="5">
-        <v>42.11</v>
+        <v>38.369999999999997</v>
       </c>
       <c r="C32" s="6">
-        <v>4288</v>
-      </c>
-      <c r="D32" s="7">
-        <v>1523</v>
-      </c>
-      <c r="E32" s="7">
-        <v>142</v>
+        <v>2500</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>40</v>
       </c>
       <c r="F32" s="7">
-        <v>142</v>
-      </c>
-      <c r="G32" s="8">
-        <f t="shared" si="0"/>
-        <v>1.5229999999999999</v>
-      </c>
-      <c r="H32" s="8">
-        <f t="shared" si="1"/>
-        <v>0.14199999999999999</v>
-      </c>
-      <c r="I32" s="9">
-        <f t="shared" si="2"/>
-        <v>10.725352112676056</v>
-      </c>
-      <c r="J32" s="10"/>
+        <v>4243</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="H32" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="I32" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="J32" s="28" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="26">
+      <c r="A34" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="30">
         <f>SUM(B5:B32)</f>
-        <v>2958.4700000000003</v>
-      </c>
-      <c r="D34" s="27">
+        <v>2958.47</v>
+      </c>
+      <c r="D34" s="31">
         <f>MAX(D5:D32)</f>
-        <v>13406</v>
-      </c>
-      <c r="G34" s="28">
+        <v>14839</v>
+      </c>
+      <c r="G34" s="32">
         <f>IFERROR(MAX(G5:G32),"")</f>
-        <v>13.406000000000001</v>
-      </c>
-      <c r="I34" s="29">
+        <v>14.839</v>
+      </c>
+      <c r="I34" s="33">
         <f>IFERROR(AVERAGE(I5:I32),"")</f>
-        <v>5.0528342641278305</v>
+        <v>10.396630018786945</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
-        <v>41</v>
+      <c r="A35" s="34" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1696,88 +1723,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
-        <v>42</v>
+      <c r="A1" s="35" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>44</v>
+      <c r="A3" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>46</v>
+      <c r="A4" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>48</v>
+      <c r="A5" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>50</v>
+      <c r="A6" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>52</v>
+      <c r="A7" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>54</v>
+      <c r="A8" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>56</v>
+      <c r="A9" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>58</v>
+      <c r="A10" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>60</v>
+      <c r="A11" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>62</v>
+      <c r="A12" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813C7AAF-87C7-4B09-91A0-470570820C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA334AF0-0008-4119-AEE6-BE7EC022EEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,43 +75,46 @@
     <t>T-04</t>
   </si>
   <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-16</t>
+  </si>
+  <si>
+    <t>T-17</t>
+  </si>
+  <si>
+    <t>P-26</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-21</t>
+  </si>
+  <si>
+    <t>T-12</t>
+  </si>
+  <si>
+    <t>T-15</t>
+  </si>
+  <si>
+    <t>T-11A</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
     <t>T-03</t>
   </si>
   <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>P-26</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-11A</t>
-  </si>
-  <si>
-    <t>T-01</t>
-  </si>
-  <si>
-    <t>T-16</t>
-  </si>
-  <si>
-    <t>T-15</t>
-  </si>
-  <si>
-    <t>T-17</t>
-  </si>
-  <si>
-    <t>T-06</t>
-  </si>
-  <si>
-    <t>T-21</t>
-  </si>
-  <si>
-    <t>T-12</t>
+    <t>T-11</t>
   </si>
   <si>
     <t>T-20</t>
@@ -129,25 +132,22 @@
     <t>T-05</t>
   </si>
   <si>
-    <t>T-11</t>
-  </si>
-  <si>
     <t>T-10A</t>
   </si>
   <si>
+    <t>T-10</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>R-08</t>
+  </si>
+  <si>
     <t>P-02</t>
-  </si>
-  <si>
-    <t>T-10</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>R-08</t>
   </si>
   <si>
     <t>T-18</t>
@@ -742,25 +742,25 @@
         <v>3352</v>
       </c>
       <c r="D5" s="7">
-        <v>11751</v>
+        <v>11739</v>
       </c>
       <c r="E5" s="7">
-        <v>10923</v>
+        <v>10911</v>
       </c>
       <c r="F5" s="7">
         <v>4020</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G32" si="0">D5/1000</f>
-        <v>11.750999999999999</v>
+        <v>11.739000000000001</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H32" si="1">E5/1000</f>
-        <v>10.923</v>
+        <v>10.911</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I32" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.9231343283582087</v>
+        <v>2.9201492537313434</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -769,130 +769,130 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>124.45</v>
+        <v>99.23</v>
       </c>
       <c r="C6" s="13">
-        <v>4845</v>
+        <v>4809</v>
       </c>
       <c r="D6" s="14">
-        <v>11165</v>
+        <v>9413</v>
       </c>
       <c r="E6" s="14">
-        <v>9750</v>
+        <v>7593</v>
       </c>
       <c r="F6" s="14">
-        <v>2795</v>
+        <v>2842</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>11.164999999999999</v>
+        <v>9.4130000000000003</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>9.75</v>
+        <v>7.593</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>3.994633273703041</v>
+        <v>3.31210415200563</v>
       </c>
       <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="12">
-        <v>133.59</v>
-      </c>
-      <c r="C7" s="13">
-        <v>4784</v>
-      </c>
-      <c r="D7" s="14">
-        <v>11165</v>
-      </c>
-      <c r="E7" s="14">
-        <v>9725</v>
-      </c>
-      <c r="F7" s="14">
-        <v>2279</v>
-      </c>
-      <c r="G7" s="15">
-        <f t="shared" si="0"/>
-        <v>11.164999999999999</v>
-      </c>
-      <c r="H7" s="15">
-        <f t="shared" si="1"/>
-        <v>9.7249999999999996</v>
-      </c>
-      <c r="I7" s="16">
-        <f t="shared" si="2"/>
-        <v>4.8990785432207105</v>
-      </c>
-      <c r="J7" s="17"/>
+      <c r="B7" s="5">
+        <v>151.93</v>
+      </c>
+      <c r="C7" s="6">
+        <v>5346</v>
+      </c>
+      <c r="D7" s="7">
+        <v>6736</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3879</v>
+      </c>
+      <c r="F7" s="7">
+        <v>2898</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="0"/>
+        <v>6.7359999999999998</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="1"/>
+        <v>3.879</v>
+      </c>
+      <c r="I7" s="9">
+        <f t="shared" si="2"/>
+        <v>2.3243616287094548</v>
+      </c>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="12">
-        <v>99.23</v>
-      </c>
-      <c r="C8" s="13">
-        <v>4809</v>
-      </c>
-      <c r="D8" s="14">
-        <v>9425</v>
-      </c>
-      <c r="E8" s="14">
-        <v>7605</v>
-      </c>
-      <c r="F8" s="14">
-        <v>2842</v>
-      </c>
-      <c r="G8" s="15">
-        <f t="shared" si="0"/>
-        <v>9.4250000000000007</v>
-      </c>
-      <c r="H8" s="15">
-        <f t="shared" si="1"/>
-        <v>7.6050000000000004</v>
-      </c>
-      <c r="I8" s="16">
-        <f t="shared" si="2"/>
-        <v>3.3163265306122449</v>
-      </c>
-      <c r="J8" s="17"/>
+      <c r="B8" s="19">
+        <v>151.26</v>
+      </c>
+      <c r="C8" s="20">
+        <v>5633</v>
+      </c>
+      <c r="D8" s="21">
+        <v>6339</v>
+      </c>
+      <c r="E8" s="21">
+        <v>3800</v>
+      </c>
+      <c r="F8" s="21">
+        <v>3546</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="0"/>
+        <v>6.3390000000000004</v>
+      </c>
+      <c r="H8" s="22">
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="2"/>
+        <v>1.787648054145516</v>
+      </c>
+      <c r="J8" s="24"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>38.369999999999997</v>
+        <v>106.47</v>
       </c>
       <c r="C9" s="6">
-        <v>2500</v>
+        <v>4634</v>
       </c>
       <c r="D9" s="7">
-        <v>8937</v>
+        <v>6209</v>
       </c>
       <c r="E9" s="7">
-        <v>8284</v>
+        <v>4653</v>
       </c>
       <c r="F9" s="7">
-        <v>4243</v>
+        <v>4379</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>8.9369999999999994</v>
+        <v>6.2089999999999996</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>8.2840000000000007</v>
+        <v>4.6529999999999996</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>2.1062927174169221</v>
+        <v>1.417903630965974</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -901,262 +901,262 @@
         <v>17</v>
       </c>
       <c r="B10" s="19">
+        <v>38.369999999999997</v>
+      </c>
+      <c r="C10" s="20">
+        <v>2500</v>
+      </c>
+      <c r="D10" s="21">
+        <v>6111</v>
+      </c>
+      <c r="E10" s="21">
+        <v>5574</v>
+      </c>
+      <c r="F10" s="21">
+        <v>4243</v>
+      </c>
+      <c r="G10" s="22">
+        <f t="shared" si="0"/>
+        <v>6.1109999999999998</v>
+      </c>
+      <c r="H10" s="22">
+        <f t="shared" si="1"/>
+        <v>5.5739999999999998</v>
+      </c>
+      <c r="I10" s="23">
+        <f t="shared" si="2"/>
+        <v>1.4402545368842801</v>
+      </c>
+      <c r="J10" s="24"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="5">
         <v>94.59</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C11" s="6">
         <v>3957</v>
       </c>
-      <c r="D10" s="21">
-        <v>8937</v>
-      </c>
-      <c r="E10" s="21">
-        <v>8410</v>
-      </c>
-      <c r="F10" s="21">
+      <c r="D11" s="7">
+        <v>6111</v>
+      </c>
+      <c r="E11" s="7">
+        <v>5548</v>
+      </c>
+      <c r="F11" s="7">
         <v>3696</v>
       </c>
-      <c r="G10" s="22">
-        <f t="shared" si="0"/>
-        <v>8.9369999999999994</v>
-      </c>
-      <c r="H10" s="22">
-        <f t="shared" si="1"/>
-        <v>8.41</v>
-      </c>
-      <c r="I10" s="23">
-        <f t="shared" si="2"/>
-        <v>2.4180194805194803</v>
-      </c>
-      <c r="J10" s="24"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="12">
-        <v>77.290000000000006</v>
-      </c>
-      <c r="C11" s="13">
-        <v>4270</v>
-      </c>
-      <c r="D11" s="14">
-        <v>8915</v>
-      </c>
-      <c r="E11" s="14">
-        <v>6446</v>
-      </c>
-      <c r="F11" s="14">
-        <v>2214</v>
-      </c>
-      <c r="G11" s="15">
-        <f t="shared" si="0"/>
-        <v>8.9149999999999991</v>
-      </c>
-      <c r="H11" s="15">
-        <f t="shared" si="1"/>
-        <v>6.4459999999999997</v>
-      </c>
-      <c r="I11" s="16">
-        <f t="shared" si="2"/>
-        <v>4.0266485998193318</v>
-      </c>
-      <c r="J11" s="17"/>
+      <c r="G11" s="8">
+        <f t="shared" si="0"/>
+        <v>6.1109999999999998</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="1"/>
+        <v>5.548</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="2"/>
+        <v>1.6534090909090908</v>
+      </c>
+      <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="19">
-        <v>151.93</v>
-      </c>
-      <c r="C12" s="20">
-        <v>5346</v>
-      </c>
-      <c r="D12" s="21">
-        <v>6749</v>
-      </c>
-      <c r="E12" s="21">
-        <v>3891</v>
-      </c>
-      <c r="F12" s="21">
-        <v>2898</v>
-      </c>
-      <c r="G12" s="22">
-        <f t="shared" si="0"/>
-        <v>6.7489999999999997</v>
-      </c>
-      <c r="H12" s="22">
-        <f t="shared" si="1"/>
-        <v>3.891</v>
-      </c>
-      <c r="I12" s="23">
-        <f t="shared" si="2"/>
-        <v>2.3288474810213939</v>
-      </c>
-      <c r="J12" s="24"/>
+      <c r="B12" s="12">
+        <v>180.3</v>
+      </c>
+      <c r="C12" s="13">
+        <v>5857</v>
+      </c>
+      <c r="D12" s="14">
+        <v>5779</v>
+      </c>
+      <c r="E12" s="14">
+        <v>2003</v>
+      </c>
+      <c r="F12" s="14">
+        <v>1530</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="0"/>
+        <v>5.7789999999999999</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="1"/>
+        <v>2.0030000000000001</v>
+      </c>
+      <c r="I12" s="16">
+        <f t="shared" si="2"/>
+        <v>3.7771241830065359</v>
+      </c>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>151.26</v>
+        <v>75.97</v>
       </c>
       <c r="C13" s="6">
-        <v>5633</v>
+        <v>3658</v>
       </c>
       <c r="D13" s="7">
-        <v>6347</v>
+        <v>5466</v>
       </c>
       <c r="E13" s="7">
-        <v>4689</v>
+        <v>3644</v>
       </c>
       <c r="F13" s="7">
-        <v>3546</v>
+        <v>2908</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>6.3470000000000004</v>
+        <v>5.4660000000000002</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>4.6890000000000001</v>
+        <v>3.6440000000000001</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.7899041173152848</v>
+        <v>1.8796423658872077</v>
       </c>
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="12">
-        <v>200.37</v>
-      </c>
-      <c r="C14" s="13">
-        <v>5776</v>
-      </c>
-      <c r="D14" s="14">
-        <v>6221</v>
-      </c>
-      <c r="E14" s="14">
-        <v>2286</v>
-      </c>
-      <c r="F14" s="14">
-        <v>2045</v>
-      </c>
-      <c r="G14" s="15">
-        <f t="shared" si="0"/>
-        <v>6.2210000000000001</v>
-      </c>
-      <c r="H14" s="15">
-        <f t="shared" si="1"/>
-        <v>2.286</v>
-      </c>
-      <c r="I14" s="16">
-        <f t="shared" si="2"/>
-        <v>3.0420537897310513</v>
-      </c>
-      <c r="J14" s="17"/>
+      <c r="B14" s="19">
+        <v>123.95</v>
+      </c>
+      <c r="C14" s="20">
+        <v>5309</v>
+      </c>
+      <c r="D14" s="21">
+        <v>5404</v>
+      </c>
+      <c r="E14" s="21">
+        <v>3800</v>
+      </c>
+      <c r="F14" s="21">
+        <v>3547</v>
+      </c>
+      <c r="G14" s="22">
+        <f t="shared" si="0"/>
+        <v>5.4039999999999999</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="2"/>
+        <v>1.5235410205807725</v>
+      </c>
+      <c r="J14" s="24"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>106.47</v>
+        <v>200.37</v>
       </c>
       <c r="C15" s="6">
-        <v>4634</v>
+        <v>5776</v>
       </c>
       <c r="D15" s="7">
-        <v>6209</v>
+        <v>5011</v>
       </c>
       <c r="E15" s="7">
-        <v>4650</v>
+        <v>2286</v>
       </c>
       <c r="F15" s="7">
-        <v>4379</v>
+        <v>2045</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>6.2089999999999996</v>
+        <v>5.0110000000000001</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>4.6500000000000004</v>
+        <v>2.286</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>1.417903630965974</v>
+        <v>2.450366748166259</v>
       </c>
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="12">
-        <v>180.3</v>
-      </c>
-      <c r="C16" s="13">
-        <v>5857</v>
-      </c>
-      <c r="D16" s="14">
-        <v>5851</v>
-      </c>
-      <c r="E16" s="14">
-        <v>2075</v>
-      </c>
-      <c r="F16" s="14">
-        <v>1530</v>
-      </c>
-      <c r="G16" s="15">
-        <f t="shared" si="0"/>
-        <v>5.851</v>
-      </c>
-      <c r="H16" s="15">
-        <f t="shared" si="1"/>
-        <v>2.0750000000000002</v>
-      </c>
-      <c r="I16" s="16">
-        <f t="shared" si="2"/>
-        <v>3.8241830065359479</v>
-      </c>
-      <c r="J16" s="17"/>
+      <c r="B16" s="19">
+        <v>77.290000000000006</v>
+      </c>
+      <c r="C16" s="20">
+        <v>4270</v>
+      </c>
+      <c r="D16" s="21">
+        <v>4990</v>
+      </c>
+      <c r="E16" s="21">
+        <v>3238</v>
+      </c>
+      <c r="F16" s="21">
+        <v>2214</v>
+      </c>
+      <c r="G16" s="22">
+        <f t="shared" si="0"/>
+        <v>4.99</v>
+      </c>
+      <c r="H16" s="22">
+        <f t="shared" si="1"/>
+        <v>3.238</v>
+      </c>
+      <c r="I16" s="23">
+        <f t="shared" si="2"/>
+        <v>2.2538392050587173</v>
+      </c>
+      <c r="J16" s="24"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>75.97</v>
+        <v>133.59</v>
       </c>
       <c r="C17" s="6">
-        <v>3658</v>
+        <v>4784</v>
       </c>
       <c r="D17" s="7">
-        <v>5474</v>
+        <v>4277</v>
       </c>
       <c r="E17" s="7">
-        <v>3652</v>
+        <v>2856</v>
       </c>
       <c r="F17" s="7">
-        <v>2908</v>
+        <v>2279</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>5.4740000000000002</v>
+        <v>4.2770000000000001</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>3.6520000000000001</v>
+        <v>2.8559999999999999</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>1.8823933975240714</v>
+        <v>1.8767003071522597</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1165,163 +1165,163 @@
         <v>25</v>
       </c>
       <c r="B18" s="19">
-        <v>123.95</v>
+        <v>124.45</v>
       </c>
       <c r="C18" s="20">
-        <v>5309</v>
+        <v>4845</v>
       </c>
       <c r="D18" s="21">
-        <v>5404</v>
+        <v>4253</v>
       </c>
       <c r="E18" s="21">
-        <v>3796</v>
+        <v>2856</v>
       </c>
       <c r="F18" s="21">
-        <v>3547</v>
+        <v>2795</v>
       </c>
       <c r="G18" s="22">
         <f t="shared" si="0"/>
-        <v>5.4039999999999999</v>
+        <v>4.2530000000000001</v>
       </c>
       <c r="H18" s="22">
         <f t="shared" si="1"/>
-        <v>3.7959999999999998</v>
+        <v>2.8559999999999999</v>
       </c>
       <c r="I18" s="23">
         <f t="shared" si="2"/>
-        <v>1.5235410205807725</v>
+        <v>1.5216457960644008</v>
       </c>
       <c r="J18" s="24"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="12">
-        <v>135.58000000000001</v>
-      </c>
-      <c r="C19" s="13">
-        <v>4844</v>
-      </c>
-      <c r="D19" s="14">
-        <v>4072</v>
-      </c>
-      <c r="E19" s="14">
-        <v>1530</v>
-      </c>
-      <c r="F19" s="14">
-        <v>1228</v>
-      </c>
-      <c r="G19" s="15">
-        <f t="shared" si="0"/>
-        <v>4.0720000000000001</v>
-      </c>
-      <c r="H19" s="15">
-        <f t="shared" si="1"/>
-        <v>1.53</v>
-      </c>
-      <c r="I19" s="16">
-        <f t="shared" si="2"/>
-        <v>3.3159609120521174</v>
-      </c>
-      <c r="J19" s="17"/>
+      <c r="B19" s="5">
+        <v>98.26</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4388</v>
+      </c>
+      <c r="D19" s="7">
+        <v>4129</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2286</v>
+      </c>
+      <c r="F19" s="7">
+        <v>2039</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>4.1289999999999996</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="1"/>
+        <v>2.286</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="2"/>
+        <v>2.0250122609122116</v>
+      </c>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>177.46</v>
+        <v>135.58000000000001</v>
       </c>
       <c r="C20" s="13">
-        <v>5465</v>
+        <v>4844</v>
       </c>
       <c r="D20" s="14">
-        <v>4069</v>
+        <v>4072</v>
       </c>
       <c r="E20" s="14">
         <v>1530</v>
       </c>
       <c r="F20" s="14">
+        <v>1228</v>
+      </c>
+      <c r="G20" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0720000000000001</v>
+      </c>
+      <c r="H20" s="15">
+        <f t="shared" si="1"/>
+        <v>1.53</v>
+      </c>
+      <c r="I20" s="16">
+        <f t="shared" si="2"/>
+        <v>3.3159609120521174</v>
+      </c>
+      <c r="J20" s="17"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="12">
+        <v>177.46</v>
+      </c>
+      <c r="C21" s="13">
+        <v>5465</v>
+      </c>
+      <c r="D21" s="14">
+        <v>4069</v>
+      </c>
+      <c r="E21" s="14">
+        <v>1530</v>
+      </c>
+      <c r="F21" s="14">
         <v>969</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G21" s="15">
         <f t="shared" si="0"/>
         <v>4.069</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H21" s="15">
         <f t="shared" si="1"/>
         <v>1.53</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I21" s="16">
         <f t="shared" si="2"/>
         <v>4.1991744066047474</v>
       </c>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="5">
-        <v>37.65</v>
-      </c>
-      <c r="C21" s="6">
-        <v>2574</v>
-      </c>
-      <c r="D21" s="7">
-        <v>3962</v>
-      </c>
-      <c r="E21" s="7">
-        <v>3088</v>
-      </c>
-      <c r="F21" s="7">
-        <v>2446</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="0"/>
-        <v>3.9620000000000002</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="1"/>
-        <v>3.0880000000000001</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="2"/>
-        <v>1.6197874080130825</v>
-      </c>
-      <c r="J21" s="10"/>
+      <c r="J21" s="17"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="19">
-        <v>37.700000000000003</v>
+        <v>37.65</v>
       </c>
       <c r="C22" s="20">
-        <v>2565</v>
+        <v>2574</v>
       </c>
       <c r="D22" s="21">
-        <v>3962</v>
+        <v>3954</v>
       </c>
       <c r="E22" s="21">
-        <v>3114</v>
+        <v>3080</v>
       </c>
       <c r="F22" s="21">
-        <v>2476</v>
+        <v>2446</v>
       </c>
       <c r="G22" s="22">
         <f t="shared" si="0"/>
-        <v>3.9620000000000002</v>
+        <v>3.9540000000000002</v>
       </c>
       <c r="H22" s="22">
         <f t="shared" si="1"/>
-        <v>3.1139999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="I22" s="23">
         <f t="shared" si="2"/>
-        <v>1.6001615508885298</v>
+        <v>1.616516762060507</v>
       </c>
       <c r="J22" s="24"/>
     </row>
@@ -1330,31 +1330,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>130.25</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="C23" s="6">
-        <v>8274</v>
+        <v>2565</v>
       </c>
       <c r="D23" s="7">
-        <v>3941</v>
+        <v>3954</v>
       </c>
       <c r="E23" s="7">
-        <v>2516</v>
+        <v>3106</v>
       </c>
       <c r="F23" s="7">
-        <v>1498</v>
+        <v>2476</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>3.9409999999999998</v>
+        <v>3.9540000000000002</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>2.516</v>
+        <v>3.1059999999999999</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>2.6308411214953269</v>
+        <v>1.5969305331179322</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1363,31 +1363,31 @@
         <v>31</v>
       </c>
       <c r="B24" s="19">
-        <v>98.26</v>
+        <v>130.25</v>
       </c>
       <c r="C24" s="20">
-        <v>4388</v>
+        <v>8274</v>
       </c>
       <c r="D24" s="21">
-        <v>3846</v>
+        <v>3929</v>
       </c>
       <c r="E24" s="21">
-        <v>2286</v>
+        <v>2504</v>
       </c>
       <c r="F24" s="21">
-        <v>2039</v>
+        <v>1498</v>
       </c>
       <c r="G24" s="22">
         <f t="shared" si="0"/>
-        <v>3.8460000000000001</v>
+        <v>3.9289999999999998</v>
       </c>
       <c r="H24" s="22">
         <f t="shared" si="1"/>
-        <v>2.286</v>
+        <v>2.504</v>
       </c>
       <c r="I24" s="23">
         <f t="shared" si="2"/>
-        <v>1.8862187346738597</v>
+        <v>2.6228304405874501</v>
       </c>
       <c r="J24" s="24"/>
     </row>
@@ -1402,7 +1402,7 @@
         <v>3448</v>
       </c>
       <c r="D25" s="7">
-        <v>3574</v>
+        <v>3596</v>
       </c>
       <c r="E25" s="7">
         <v>3186</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>3.5739999999999998</v>
+        <v>3.5960000000000001</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>2.3405370006548787</v>
+        <v>2.35494433529797</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1429,31 +1429,31 @@
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>78.38</v>
+        <v>156.94</v>
       </c>
       <c r="C26" s="13">
-        <v>4052</v>
+        <v>5252</v>
       </c>
       <c r="D26" s="14">
-        <v>3380</v>
+        <v>3238</v>
       </c>
       <c r="E26" s="14">
-        <v>3033</v>
+        <v>760</v>
       </c>
       <c r="F26" s="14">
-        <v>767</v>
+        <v>567</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>3.38</v>
+        <v>3.238</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>3.0329999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>4.406779661016949</v>
+        <v>5.7107583774250443</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1462,31 +1462,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="12">
-        <v>156.94</v>
+        <v>103.71</v>
       </c>
       <c r="C27" s="13">
-        <v>5252</v>
+        <v>4418</v>
       </c>
       <c r="D27" s="14">
-        <v>3238</v>
+        <v>3058</v>
       </c>
       <c r="E27" s="14">
-        <v>760</v>
+        <v>547</v>
       </c>
       <c r="F27" s="14">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="G27" s="15">
         <f t="shared" si="0"/>
-        <v>3.238</v>
+        <v>3.0579999999999998</v>
       </c>
       <c r="H27" s="15">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="I27" s="16">
         <f t="shared" si="2"/>
-        <v>5.7107583774250443</v>
+        <v>5.6007326007326004</v>
       </c>
       <c r="J27" s="17"/>
     </row>
@@ -1495,31 +1495,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>103.71</v>
+        <v>182.48</v>
       </c>
       <c r="C28" s="13">
-        <v>4418</v>
+        <v>5481</v>
       </c>
       <c r="D28" s="14">
-        <v>3058</v>
+        <v>2553</v>
       </c>
       <c r="E28" s="14">
-        <v>760</v>
+        <v>254</v>
       </c>
       <c r="F28" s="14">
-        <v>546</v>
+        <v>291</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>3.0579999999999998</v>
+        <v>2.5529999999999999</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>0.254</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>5.6007326007326004</v>
+        <v>8.7731958762886606</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1528,66 +1528,66 @@
         <v>36</v>
       </c>
       <c r="B29" s="12">
-        <v>182.48</v>
+        <v>53.1</v>
       </c>
       <c r="C29" s="13">
-        <v>5481</v>
+        <v>3752</v>
       </c>
       <c r="D29" s="14">
-        <v>2565</v>
+        <v>1940</v>
       </c>
       <c r="E29" s="14">
-        <v>254</v>
+        <v>629</v>
       </c>
       <c r="F29" s="14">
-        <v>291</v>
+        <v>121</v>
       </c>
       <c r="G29" s="15">
         <f t="shared" si="0"/>
-        <v>2.5649999999999999</v>
+        <v>1.94</v>
       </c>
       <c r="H29" s="15">
         <f t="shared" si="1"/>
-        <v>0.254</v>
+        <v>0.629</v>
       </c>
       <c r="I29" s="16">
         <f t="shared" si="2"/>
-        <v>8.8144329896907223</v>
+        <v>16.033057851239668</v>
       </c>
       <c r="J29" s="17"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="12">
-        <v>53.1</v>
-      </c>
-      <c r="C30" s="13">
-        <v>3752</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1964</v>
-      </c>
-      <c r="E30" s="14">
-        <v>629</v>
-      </c>
-      <c r="F30" s="14">
-        <v>121</v>
-      </c>
-      <c r="G30" s="15">
-        <f t="shared" si="0"/>
-        <v>1.964</v>
-      </c>
-      <c r="H30" s="15">
-        <f t="shared" si="1"/>
-        <v>0.629</v>
-      </c>
-      <c r="I30" s="16">
-        <f t="shared" si="2"/>
-        <v>16.231404958677686</v>
-      </c>
-      <c r="J30" s="17"/>
+      <c r="B30" s="19">
+        <v>78.38</v>
+      </c>
+      <c r="C30" s="20">
+        <v>4052</v>
+      </c>
+      <c r="D30" s="21">
+        <v>1559</v>
+      </c>
+      <c r="E30" s="21">
+        <v>968</v>
+      </c>
+      <c r="F30" s="21">
+        <v>767</v>
+      </c>
+      <c r="G30" s="22">
+        <f t="shared" si="0"/>
+        <v>1.5589999999999999</v>
+      </c>
+      <c r="H30" s="22">
+        <f t="shared" si="1"/>
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="I30" s="23">
+        <f t="shared" si="2"/>
+        <v>2.0325945241199479</v>
+      </c>
+      <c r="J30" s="24"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
@@ -1633,7 +1633,7 @@
         <v>4288</v>
       </c>
       <c r="D32" s="14">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="E32" s="14">
         <v>228</v>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>1.2769999999999999</v>
+        <v>1.2649999999999999</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>8.9929577464788739</v>
+        <v>8.908450704225352</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1661,19 +1661,19 @@
       </c>
       <c r="B34" s="26">
         <f>SUM(B5:B32)</f>
-        <v>2958.4700000000012</v>
+        <v>2958.4700000000003</v>
       </c>
       <c r="D34" s="27">
         <f>MAX(D5:D32)</f>
-        <v>11751</v>
+        <v>11739</v>
       </c>
       <c r="G34" s="28">
         <f>IFERROR(MAX(G5:G32),"")</f>
-        <v>11.750999999999999</v>
+        <v>11.739000000000001</v>
       </c>
       <c r="I34" s="29">
         <f>IFERROR(AVERAGE(I5:I32),"")</f>
-        <v>3.9335246597289157</v>
+        <v>3.508029737307587</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA334AF0-0008-4119-AEE6-BE7EC022EEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83543E1-E3F8-46EE-98C8-98F34A4E7F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83543E1-E3F8-46EE-98C8-98F34A4E7F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ACDF6C-0D4A-4E1E-8D8D-9AD4A6AC2763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,54 +81,54 @@
     <t>T-01</t>
   </si>
   <si>
+    <t>P-26</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-17</t>
+  </si>
+  <si>
     <t>T-16</t>
   </si>
   <si>
-    <t>T-17</t>
-  </si>
-  <si>
-    <t>P-26</t>
-  </si>
-  <si>
-    <t>T-08</t>
+    <t>T-07</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-12</t>
+  </si>
+  <si>
+    <t>T-21</t>
   </si>
   <si>
     <t>T-06</t>
   </si>
   <si>
-    <t>T-21</t>
-  </si>
-  <si>
-    <t>T-12</t>
+    <t>T-11A</t>
   </si>
   <si>
     <t>T-15</t>
   </si>
   <si>
-    <t>T-11A</t>
-  </si>
-  <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-03</t>
+    <t>T-21R</t>
+  </si>
+  <si>
+    <t>A-01</t>
   </si>
   <si>
     <t>T-11</t>
   </si>
   <si>
+    <t>T-19</t>
+  </si>
+  <si>
     <t>T-20</t>
   </si>
   <si>
-    <t>T-19</t>
-  </si>
-  <si>
-    <t>A-01</t>
-  </si>
-  <si>
-    <t>T-21R</t>
-  </si>
-  <si>
     <t>T-05</t>
   </si>
   <si>
@@ -144,16 +144,16 @@
     <t>T-09</t>
   </si>
   <si>
+    <t>P-02</t>
+  </si>
+  <si>
+    <t>T-18</t>
+  </si>
+  <si>
+    <t>T-13</t>
+  </si>
+  <si>
     <t>R-08</t>
-  </si>
-  <si>
-    <t>P-02</t>
-  </si>
-  <si>
-    <t>T-18</t>
-  </si>
-  <si>
-    <t>T-13</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -808,7 +808,7 @@
         <v>5346</v>
       </c>
       <c r="D7" s="7">
-        <v>6736</v>
+        <v>6737</v>
       </c>
       <c r="E7" s="7">
         <v>3879</v>
@@ -818,7 +818,7 @@
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>6.7359999999999998</v>
+        <v>6.7370000000000001</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>2.3243616287094548</v>
+        <v>2.3247066942719115</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -835,31 +835,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="19">
-        <v>151.26</v>
+        <v>38.369999999999997</v>
       </c>
       <c r="C8" s="20">
-        <v>5633</v>
+        <v>2500</v>
       </c>
       <c r="D8" s="21">
-        <v>6339</v>
+        <v>6552</v>
       </c>
       <c r="E8" s="21">
-        <v>3800</v>
+        <v>5899</v>
       </c>
       <c r="F8" s="21">
-        <v>3546</v>
+        <v>4243</v>
       </c>
       <c r="G8" s="22">
         <f t="shared" si="0"/>
-        <v>6.3390000000000004</v>
+        <v>6.5519999999999996</v>
       </c>
       <c r="H8" s="22">
         <f t="shared" si="1"/>
-        <v>3.8</v>
+        <v>5.899</v>
       </c>
       <c r="I8" s="23">
         <f t="shared" si="2"/>
-        <v>1.787648054145516</v>
+        <v>1.5441904312986094</v>
       </c>
       <c r="J8" s="24"/>
     </row>
@@ -868,31 +868,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>106.47</v>
+        <v>94.59</v>
       </c>
       <c r="C9" s="6">
-        <v>4634</v>
+        <v>3957</v>
       </c>
       <c r="D9" s="7">
-        <v>6209</v>
+        <v>6552</v>
       </c>
       <c r="E9" s="7">
-        <v>4653</v>
+        <v>6024</v>
       </c>
       <c r="F9" s="7">
-        <v>4379</v>
+        <v>3696</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>6.2089999999999996</v>
+        <v>6.5519999999999996</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>4.6529999999999996</v>
+        <v>6.024</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>1.417903630965974</v>
+        <v>1.7727272727272727</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -901,31 +901,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="19">
-        <v>38.369999999999997</v>
+        <v>106.47</v>
       </c>
       <c r="C10" s="20">
-        <v>2500</v>
+        <v>4634</v>
       </c>
       <c r="D10" s="21">
-        <v>6111</v>
+        <v>6209</v>
       </c>
       <c r="E10" s="21">
-        <v>5574</v>
+        <v>4653</v>
       </c>
       <c r="F10" s="21">
-        <v>4243</v>
+        <v>4379</v>
       </c>
       <c r="G10" s="22">
         <f t="shared" si="0"/>
-        <v>6.1109999999999998</v>
+        <v>6.2089999999999996</v>
       </c>
       <c r="H10" s="22">
         <f t="shared" si="1"/>
-        <v>5.5739999999999998</v>
+        <v>4.6529999999999996</v>
       </c>
       <c r="I10" s="23">
         <f t="shared" si="2"/>
-        <v>1.4402545368842801</v>
+        <v>1.417903630965974</v>
       </c>
       <c r="J10" s="24"/>
     </row>
@@ -934,97 +934,97 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>94.59</v>
+        <v>151.26</v>
       </c>
       <c r="C11" s="6">
-        <v>3957</v>
+        <v>5633</v>
       </c>
       <c r="D11" s="7">
-        <v>6111</v>
+        <v>6186</v>
       </c>
       <c r="E11" s="7">
-        <v>5548</v>
+        <v>3800</v>
       </c>
       <c r="F11" s="7">
-        <v>3696</v>
+        <v>3546</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>6.1109999999999998</v>
+        <v>6.1859999999999999</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>5.548</v>
+        <v>3.8</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.6534090909090908</v>
+        <v>1.7445008460236886</v>
       </c>
       <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="12">
-        <v>180.3</v>
-      </c>
-      <c r="C12" s="13">
-        <v>5857</v>
-      </c>
-      <c r="D12" s="14">
-        <v>5779</v>
-      </c>
-      <c r="E12" s="14">
-        <v>2003</v>
-      </c>
-      <c r="F12" s="14">
-        <v>1530</v>
-      </c>
-      <c r="G12" s="15">
-        <f t="shared" si="0"/>
-        <v>5.7789999999999999</v>
-      </c>
-      <c r="H12" s="15">
-        <f t="shared" si="1"/>
-        <v>2.0030000000000001</v>
-      </c>
-      <c r="I12" s="16">
-        <f t="shared" si="2"/>
-        <v>3.7771241830065359</v>
-      </c>
-      <c r="J12" s="17"/>
+      <c r="B12" s="19">
+        <v>133.59</v>
+      </c>
+      <c r="C12" s="20">
+        <v>4784</v>
+      </c>
+      <c r="D12" s="21">
+        <v>5885</v>
+      </c>
+      <c r="E12" s="21">
+        <v>3420</v>
+      </c>
+      <c r="F12" s="21">
+        <v>2279</v>
+      </c>
+      <c r="G12" s="22">
+        <f t="shared" si="0"/>
+        <v>5.8849999999999998</v>
+      </c>
+      <c r="H12" s="22">
+        <f t="shared" si="1"/>
+        <v>3.42</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="2"/>
+        <v>2.5822729267222466</v>
+      </c>
+      <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>75.97</v>
+        <v>124.45</v>
       </c>
       <c r="C13" s="6">
-        <v>3658</v>
+        <v>4845</v>
       </c>
       <c r="D13" s="7">
-        <v>5466</v>
+        <v>5861</v>
       </c>
       <c r="E13" s="7">
-        <v>3644</v>
+        <v>4357</v>
       </c>
       <c r="F13" s="7">
-        <v>2908</v>
+        <v>2795</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>5.4660000000000002</v>
+        <v>5.8609999999999998</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>3.6440000000000001</v>
+        <v>4.3570000000000002</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.8796423658872077</v>
+        <v>2.0969588550983902</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1066,97 +1066,97 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>200.37</v>
+        <v>75.97</v>
       </c>
       <c r="C15" s="6">
-        <v>5776</v>
+        <v>3658</v>
       </c>
       <c r="D15" s="7">
-        <v>5011</v>
+        <v>5336</v>
       </c>
       <c r="E15" s="7">
-        <v>2286</v>
+        <v>3504</v>
       </c>
       <c r="F15" s="7">
-        <v>2045</v>
+        <v>2908</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>5.0110000000000001</v>
+        <v>5.3360000000000003</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>2.286</v>
+        <v>3.504</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>2.450366748166259</v>
+        <v>1.8349381017881705</v>
       </c>
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="19">
-        <v>77.290000000000006</v>
-      </c>
-      <c r="C16" s="20">
-        <v>4270</v>
-      </c>
-      <c r="D16" s="21">
-        <v>4990</v>
-      </c>
-      <c r="E16" s="21">
-        <v>3238</v>
-      </c>
-      <c r="F16" s="21">
-        <v>2214</v>
-      </c>
-      <c r="G16" s="22">
-        <f t="shared" si="0"/>
-        <v>4.99</v>
-      </c>
-      <c r="H16" s="22">
-        <f t="shared" si="1"/>
-        <v>3.238</v>
-      </c>
-      <c r="I16" s="23">
-        <f t="shared" si="2"/>
-        <v>2.2538392050587173</v>
-      </c>
-      <c r="J16" s="24"/>
+      <c r="B16" s="12">
+        <v>180.3</v>
+      </c>
+      <c r="C16" s="13">
+        <v>5857</v>
+      </c>
+      <c r="D16" s="14">
+        <v>5161</v>
+      </c>
+      <c r="E16" s="14">
+        <v>2003</v>
+      </c>
+      <c r="F16" s="14">
+        <v>1530</v>
+      </c>
+      <c r="G16" s="15">
+        <f t="shared" si="0"/>
+        <v>5.1609999999999996</v>
+      </c>
+      <c r="H16" s="15">
+        <f t="shared" si="1"/>
+        <v>2.0030000000000001</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="2"/>
+        <v>3.373202614379085</v>
+      </c>
+      <c r="J16" s="17"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>133.59</v>
+        <v>77.290000000000006</v>
       </c>
       <c r="C17" s="6">
-        <v>4784</v>
+        <v>4270</v>
       </c>
       <c r="D17" s="7">
-        <v>4277</v>
+        <v>4990</v>
       </c>
       <c r="E17" s="7">
-        <v>2856</v>
+        <v>3238</v>
       </c>
       <c r="F17" s="7">
-        <v>2279</v>
+        <v>2214</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>4.2770000000000001</v>
+        <v>4.99</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>2.8559999999999999</v>
+        <v>3.238</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>1.8767003071522597</v>
+        <v>2.2538392050587173</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1165,31 +1165,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="19">
-        <v>124.45</v>
+        <v>200.37</v>
       </c>
       <c r="C18" s="20">
-        <v>4845</v>
+        <v>5776</v>
       </c>
       <c r="D18" s="21">
-        <v>4253</v>
+        <v>4942</v>
       </c>
       <c r="E18" s="21">
-        <v>2856</v>
+        <v>2286</v>
       </c>
       <c r="F18" s="21">
-        <v>2795</v>
+        <v>2045</v>
       </c>
       <c r="G18" s="22">
         <f t="shared" si="0"/>
-        <v>4.2530000000000001</v>
+        <v>4.9420000000000002</v>
       </c>
       <c r="H18" s="22">
         <f t="shared" si="1"/>
-        <v>2.8559999999999999</v>
+        <v>2.286</v>
       </c>
       <c r="I18" s="23">
         <f t="shared" si="2"/>
-        <v>1.5216457960644008</v>
+        <v>2.4166259168704158</v>
       </c>
       <c r="J18" s="24"/>
     </row>
@@ -1198,165 +1198,165 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2565</v>
+      </c>
+      <c r="D19" s="7">
+        <v>4375</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3053</v>
+      </c>
+      <c r="F19" s="7">
+        <v>2476</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>4.375</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="1"/>
+        <v>3.0529999999999999</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="2"/>
+        <v>1.7669628432956381</v>
+      </c>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="19">
+        <v>37.65</v>
+      </c>
+      <c r="C20" s="20">
+        <v>2574</v>
+      </c>
+      <c r="D20" s="21">
+        <v>4332</v>
+      </c>
+      <c r="E20" s="21">
+        <v>3027</v>
+      </c>
+      <c r="F20" s="21">
+        <v>2446</v>
+      </c>
+      <c r="G20" s="22">
+        <f t="shared" si="0"/>
+        <v>4.3319999999999999</v>
+      </c>
+      <c r="H20" s="22">
+        <f t="shared" si="1"/>
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="2"/>
+        <v>1.7710547833197057</v>
+      </c>
+      <c r="J20" s="24"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="5">
         <v>98.26</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C21" s="6">
         <v>4388</v>
       </c>
-      <c r="D19" s="7">
-        <v>4129</v>
-      </c>
-      <c r="E19" s="7">
+      <c r="D21" s="7">
+        <v>4108</v>
+      </c>
+      <c r="E21" s="7">
         <v>2286</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F21" s="7">
         <v>2039</v>
       </c>
-      <c r="G19" s="8">
-        <f t="shared" si="0"/>
-        <v>4.1289999999999996</v>
-      </c>
-      <c r="H19" s="8">
+      <c r="G21" s="8">
+        <f t="shared" si="0"/>
+        <v>4.1079999999999997</v>
+      </c>
+      <c r="H21" s="8">
         <f t="shared" si="1"/>
         <v>2.286</v>
       </c>
-      <c r="I19" s="9">
-        <f t="shared" si="2"/>
-        <v>2.0250122609122116</v>
-      </c>
-      <c r="J19" s="10"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="12">
+      <c r="I21" s="9">
+        <f t="shared" si="2"/>
+        <v>2.0147130946542422</v>
+      </c>
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="12">
+        <v>177.46</v>
+      </c>
+      <c r="C22" s="13">
+        <v>5465</v>
+      </c>
+      <c r="D22" s="14">
+        <v>4063</v>
+      </c>
+      <c r="E22" s="14">
+        <v>1523</v>
+      </c>
+      <c r="F22" s="14">
+        <v>969</v>
+      </c>
+      <c r="G22" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0629999999999997</v>
+      </c>
+      <c r="H22" s="15">
+        <f t="shared" si="1"/>
+        <v>1.5229999999999999</v>
+      </c>
+      <c r="I22" s="16">
+        <f t="shared" si="2"/>
+        <v>4.192982456140351</v>
+      </c>
+      <c r="J22" s="17"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="12">
         <v>135.58000000000001</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C23" s="13">
         <v>4844</v>
       </c>
-      <c r="D20" s="14">
-        <v>4072</v>
-      </c>
-      <c r="E20" s="14">
-        <v>1530</v>
-      </c>
-      <c r="F20" s="14">
+      <c r="D23" s="14">
+        <v>3981</v>
+      </c>
+      <c r="E23" s="14">
+        <v>1523</v>
+      </c>
+      <c r="F23" s="14">
         <v>1228</v>
       </c>
-      <c r="G20" s="15">
-        <f t="shared" si="0"/>
-        <v>4.0720000000000001</v>
-      </c>
-      <c r="H20" s="15">
-        <f t="shared" si="1"/>
-        <v>1.53</v>
-      </c>
-      <c r="I20" s="16">
-        <f t="shared" si="2"/>
-        <v>3.3159609120521174</v>
-      </c>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="12">
-        <v>177.46</v>
-      </c>
-      <c r="C21" s="13">
-        <v>5465</v>
-      </c>
-      <c r="D21" s="14">
-        <v>4069</v>
-      </c>
-      <c r="E21" s="14">
-        <v>1530</v>
-      </c>
-      <c r="F21" s="14">
-        <v>969</v>
-      </c>
-      <c r="G21" s="15">
-        <f t="shared" si="0"/>
-        <v>4.069</v>
-      </c>
-      <c r="H21" s="15">
-        <f t="shared" si="1"/>
-        <v>1.53</v>
-      </c>
-      <c r="I21" s="16">
-        <f t="shared" si="2"/>
-        <v>4.1991744066047474</v>
-      </c>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="19">
-        <v>37.65</v>
-      </c>
-      <c r="C22" s="20">
-        <v>2574</v>
-      </c>
-      <c r="D22" s="21">
-        <v>3954</v>
-      </c>
-      <c r="E22" s="21">
-        <v>3080</v>
-      </c>
-      <c r="F22" s="21">
-        <v>2446</v>
-      </c>
-      <c r="G22" s="22">
-        <f t="shared" si="0"/>
-        <v>3.9540000000000002</v>
-      </c>
-      <c r="H22" s="22">
-        <f t="shared" si="1"/>
-        <v>3.08</v>
-      </c>
-      <c r="I22" s="23">
-        <f t="shared" si="2"/>
-        <v>1.616516762060507</v>
-      </c>
-      <c r="J22" s="24"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="5">
-        <v>37.700000000000003</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2565</v>
-      </c>
-      <c r="D23" s="7">
-        <v>3954</v>
-      </c>
-      <c r="E23" s="7">
-        <v>3106</v>
-      </c>
-      <c r="F23" s="7">
-        <v>2476</v>
-      </c>
-      <c r="G23" s="8">
-        <f t="shared" si="0"/>
-        <v>3.9540000000000002</v>
-      </c>
-      <c r="H23" s="8">
-        <f t="shared" si="1"/>
-        <v>3.1059999999999999</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="2"/>
-        <v>1.5969305331179322</v>
-      </c>
-      <c r="J23" s="10"/>
+      <c r="G23" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9809999999999999</v>
+      </c>
+      <c r="H23" s="15">
+        <f t="shared" si="1"/>
+        <v>1.5229999999999999</v>
+      </c>
+      <c r="I23" s="16">
+        <f t="shared" si="2"/>
+        <v>3.2418566775244302</v>
+      </c>
+      <c r="J23" s="17"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
@@ -1468,7 +1468,7 @@
         <v>4418</v>
       </c>
       <c r="D27" s="14">
-        <v>3058</v>
+        <v>2865</v>
       </c>
       <c r="E27" s="14">
         <v>547</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G27" s="15">
         <f t="shared" si="0"/>
-        <v>3.0579999999999998</v>
+        <v>2.8650000000000002</v>
       </c>
       <c r="H27" s="15">
         <f t="shared" si="1"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="I27" s="16">
         <f t="shared" si="2"/>
-        <v>5.6007326007326004</v>
+        <v>5.2472527472527473</v>
       </c>
       <c r="J27" s="17"/>
     </row>
@@ -1524,101 +1524,101 @@
       <c r="J28" s="17"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="12">
-        <v>53.1</v>
-      </c>
-      <c r="C29" s="13">
-        <v>3752</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1940</v>
-      </c>
-      <c r="E29" s="14">
-        <v>629</v>
-      </c>
-      <c r="F29" s="14">
-        <v>121</v>
-      </c>
-      <c r="G29" s="15">
-        <f t="shared" si="0"/>
-        <v>1.94</v>
-      </c>
-      <c r="H29" s="15">
-        <f t="shared" si="1"/>
-        <v>0.629</v>
-      </c>
-      <c r="I29" s="16">
-        <f t="shared" si="2"/>
-        <v>16.033057851239668</v>
-      </c>
-      <c r="J29" s="17"/>
+      <c r="B29" s="5">
+        <v>78.38</v>
+      </c>
+      <c r="C29" s="6">
+        <v>4052</v>
+      </c>
+      <c r="D29" s="7">
+        <v>1552</v>
+      </c>
+      <c r="E29" s="7">
+        <v>962</v>
+      </c>
+      <c r="F29" s="7">
+        <v>767</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="0"/>
+        <v>1.552</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="1"/>
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="I29" s="9">
+        <f t="shared" si="2"/>
+        <v>2.0234680573663626</v>
+      </c>
+      <c r="J29" s="10"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="19">
-        <v>78.38</v>
-      </c>
-      <c r="C30" s="20">
-        <v>4052</v>
-      </c>
-      <c r="D30" s="21">
-        <v>1559</v>
-      </c>
-      <c r="E30" s="21">
-        <v>968</v>
-      </c>
-      <c r="F30" s="21">
-        <v>767</v>
-      </c>
-      <c r="G30" s="22">
-        <f t="shared" si="0"/>
-        <v>1.5589999999999999</v>
-      </c>
-      <c r="H30" s="22">
-        <f t="shared" si="1"/>
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="I30" s="23">
-        <f t="shared" si="2"/>
-        <v>2.0325945241199479</v>
-      </c>
-      <c r="J30" s="24"/>
+      <c r="B30" s="12">
+        <v>72.67</v>
+      </c>
+      <c r="C30" s="13">
+        <v>4022</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1552</v>
+      </c>
+      <c r="E30" s="14">
+        <v>989</v>
+      </c>
+      <c r="F30" s="14">
+        <v>473</v>
+      </c>
+      <c r="G30" s="15">
+        <f t="shared" si="0"/>
+        <v>1.552</v>
+      </c>
+      <c r="H30" s="15">
+        <f t="shared" si="1"/>
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="I30" s="16">
+        <f t="shared" si="2"/>
+        <v>3.2811839323467229</v>
+      </c>
+      <c r="J30" s="17"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B31" s="12">
-        <v>72.67</v>
+        <v>42.11</v>
       </c>
       <c r="C31" s="13">
-        <v>4022</v>
+        <v>4288</v>
       </c>
       <c r="D31" s="14">
-        <v>1559</v>
+        <v>1265</v>
       </c>
       <c r="E31" s="14">
-        <v>995</v>
+        <v>228</v>
       </c>
       <c r="F31" s="14">
-        <v>473</v>
+        <v>142</v>
       </c>
       <c r="G31" s="15">
         <f t="shared" si="0"/>
-        <v>1.5589999999999999</v>
+        <v>1.2649999999999999</v>
       </c>
       <c r="H31" s="15">
         <f t="shared" si="1"/>
-        <v>0.995</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="I31" s="16">
         <f t="shared" si="2"/>
-        <v>3.2959830866807609</v>
+        <v>8.908450704225352</v>
       </c>
       <c r="J31" s="17"/>
     </row>
@@ -1627,31 +1627,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>42.11</v>
+        <v>53.1</v>
       </c>
       <c r="C32" s="13">
-        <v>4288</v>
+        <v>3752</v>
       </c>
       <c r="D32" s="14">
-        <v>1265</v>
+        <v>1089</v>
       </c>
       <c r="E32" s="14">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="F32" s="14">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>1.2649999999999999</v>
+        <v>1.089</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>0.22800000000000001</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>8.908450704225352</v>
+        <v>9</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B34" s="26">
         <f>SUM(B5:B32)</f>
-        <v>2958.4700000000003</v>
+        <v>2958.4700000000007</v>
       </c>
       <c r="D34" s="27">
         <f>MAX(D5:D32)</f>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="I34" s="29">
         <f>IFERROR(AVERAGE(I5:I32),"")</f>
-        <v>3.508029737307587</v>
+        <v>3.2866898302588177</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ACDF6C-0D4A-4E1E-8D8D-9AD4A6AC2763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB3039B-164B-4D90-AE11-F73633C279E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB3039B-164B-4D90-AE11-F73633C279E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C338B00E-43F5-4051-A2A4-E00722CD39D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C338B00E-43F5-4051-A2A4-E00722CD39D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EED8FA5-F814-4C19-9BBD-1536BB8DEBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EED8FA5-F814-4C19-9BBD-1536BB8DEBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A103655-597E-4780-B5A1-F195D30DD008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,49 +244,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A103655-597E-4780-B5A1-F195D30DD008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5194CE5E-F36C-4498-BA84-C24870D6A82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -244,58 +244,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5194CE5E-F36C-4498-BA84-C24870D6A82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EA18E0-53F6-46CA-83EC-22C0F5E8227D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -244,49 +244,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EA18E0-53F6-46CA-83EC-22C0F5E8227D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D00D802-83F3-4FC3-966A-EB489A1BC5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_MATO_GROSSO_distancias.xlsx
+++ b/FAZENDA_MATO_GROSSO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D00D802-83F3-4FC3-966A-EB489A1BC5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2E341C-7405-4421-9740-0B9BF6E5EEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -244,58 +244,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
